--- a/datasheets/MasterList forestreserves.xlsx
+++ b/datasheets/MasterList forestreserves.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\1. Journalism (GDrive)\1. Forest Reserve Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yao Hua\Documents\GitHub\fate_forest_data_repository\datasheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D929CD54-B421-4D20-BB60-526AB77C7F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7581996B-2A01-4BEF-A662-8320F041F634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{D42950D3-1CFB-4496-995B-90318C407A2F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="901">
   <si>
     <t>no</t>
   </si>
@@ -2733,6 +2733,12 @@
   </si>
   <si>
     <t>LastUpdated: 2026/4/12</t>
+  </si>
+  <si>
+    <t>Parit Dayong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First mention of 'Parit Dayong' in Perak.2026.3144. </t>
   </si>
 </sst>
 </file>
@@ -3251,27 +3257,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3307,6 +3292,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3677,22 +3683,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="43" t="s">
         <v>898</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="33" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="45" t="s">
         <v>888</v>
       </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="36" t="s">
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="48" t="s">
         <v>889</v>
       </c>
-      <c r="J1" s="37"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="23" t="s">
@@ -3716,7 +3722,7 @@
       <c r="G2" s="26" t="s">
         <v>771</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="38" t="s">
         <v>896</v>
       </c>
       <c r="I2" s="27" t="s">
@@ -3748,7 +3754,7 @@
       <c r="G3" s="20">
         <v>0</v>
       </c>
-      <c r="H3" s="46"/>
+      <c r="H3" s="39"/>
       <c r="I3" s="21" t="s">
         <v>2</v>
       </c>
@@ -3776,7 +3782,7 @@
       <c r="G4" s="9">
         <v>0</v>
       </c>
-      <c r="H4" s="47"/>
+      <c r="H4" s="40"/>
       <c r="I4" s="13"/>
       <c r="J4" s="14"/>
       <c r="V4" s="1"/>
@@ -3803,7 +3809,7 @@
       <c r="G5" s="9">
         <v>0</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="40"/>
       <c r="I5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3832,7 +3838,7 @@
       <c r="G6" s="9">
         <v>0</v>
       </c>
-      <c r="H6" s="47"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="13"/>
       <c r="J6" s="14"/>
       <c r="V6" s="1"/>
@@ -3859,7 +3865,7 @@
       <c r="G7" s="9">
         <v>0</v>
       </c>
-      <c r="H7" s="47"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
       <c r="V7" s="1"/>
@@ -3886,7 +3892,7 @@
       <c r="G8" s="9">
         <v>0</v>
       </c>
-      <c r="H8" s="47"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="13"/>
       <c r="J8" s="14" t="s">
         <v>774</v>
@@ -3915,7 +3921,7 @@
       <c r="G9" s="9">
         <v>0</v>
       </c>
-      <c r="H9" s="47"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="13"/>
       <c r="J9" s="14" t="s">
         <v>775</v>
@@ -3944,7 +3950,7 @@
       <c r="G10" s="9">
         <v>0</v>
       </c>
-      <c r="H10" s="47"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="13"/>
       <c r="J10" s="14" t="s">
         <v>776</v>
@@ -3973,7 +3979,7 @@
       <c r="G11" s="9">
         <v>0</v>
       </c>
-      <c r="H11" s="47"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="13"/>
       <c r="J11" s="14"/>
     </row>
@@ -3999,7 +4005,7 @@
       <c r="G12" s="9">
         <v>0</v>
       </c>
-      <c r="H12" s="47"/>
+      <c r="H12" s="40"/>
       <c r="I12" s="13"/>
       <c r="J12" s="14"/>
     </row>
@@ -4025,7 +4031,7 @@
       <c r="G13" s="9">
         <v>0</v>
       </c>
-      <c r="H13" s="47"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="13" t="s">
         <v>760</v>
       </c>
@@ -4055,7 +4061,7 @@
       <c r="G14" s="9">
         <v>0</v>
       </c>
-      <c r="H14" s="47"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="13"/>
       <c r="J14" s="14"/>
     </row>
@@ -4081,7 +4087,7 @@
       <c r="G15" s="9">
         <v>0</v>
       </c>
-      <c r="H15" s="47"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="13"/>
       <c r="J15" s="14" t="s">
         <v>777</v>
@@ -4109,7 +4115,7 @@
       <c r="G16" s="9">
         <v>0</v>
       </c>
-      <c r="H16" s="47"/>
+      <c r="H16" s="40"/>
       <c r="I16" s="13" t="s">
         <v>19</v>
       </c>
@@ -4137,7 +4143,7 @@
       <c r="G17" s="9">
         <v>0</v>
       </c>
-      <c r="H17" s="47"/>
+      <c r="H17" s="40"/>
       <c r="I17" s="13" t="s">
         <v>21</v>
       </c>
@@ -4167,7 +4173,7 @@
       <c r="G18" s="9">
         <v>0</v>
       </c>
-      <c r="H18" s="47"/>
+      <c r="H18" s="40"/>
       <c r="I18" s="13"/>
       <c r="J18" s="14"/>
     </row>
@@ -4193,7 +4199,7 @@
       <c r="G19" s="9">
         <v>0</v>
       </c>
-      <c r="H19" s="47"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="13"/>
       <c r="J19" s="14"/>
     </row>
@@ -4219,7 +4225,7 @@
       <c r="G20" s="9">
         <v>0</v>
       </c>
-      <c r="H20" s="47"/>
+      <c r="H20" s="40"/>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
     </row>
@@ -4245,7 +4251,7 @@
       <c r="G21" s="9">
         <v>0</v>
       </c>
-      <c r="H21" s="47"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="13"/>
       <c r="J21" s="14"/>
     </row>
@@ -4271,7 +4277,7 @@
       <c r="G22" s="9">
         <v>0</v>
       </c>
-      <c r="H22" s="47"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="13"/>
       <c r="J22" s="14"/>
     </row>
@@ -4297,7 +4303,7 @@
       <c r="G23" s="9">
         <v>0</v>
       </c>
-      <c r="H23" s="47"/>
+      <c r="H23" s="40"/>
       <c r="I23" s="13"/>
       <c r="J23" s="14"/>
     </row>
@@ -4323,7 +4329,7 @@
       <c r="G24" s="9">
         <v>0</v>
       </c>
-      <c r="H24" s="47"/>
+      <c r="H24" s="40"/>
       <c r="I24" s="13"/>
       <c r="J24" s="14" t="s">
         <v>779</v>
@@ -4351,7 +4357,7 @@
       <c r="G25" s="9">
         <v>0</v>
       </c>
-      <c r="H25" s="47"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="13" t="s">
         <v>30</v>
       </c>
@@ -4379,7 +4385,7 @@
       <c r="G26" s="9">
         <v>0</v>
       </c>
-      <c r="H26" s="47"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="13"/>
       <c r="J26" s="14"/>
     </row>
@@ -4405,7 +4411,7 @@
       <c r="G27" s="9">
         <v>0</v>
       </c>
-      <c r="H27" s="47"/>
+      <c r="H27" s="40"/>
       <c r="I27" s="13" t="s">
         <v>33</v>
       </c>
@@ -4435,7 +4441,7 @@
       <c r="G28" s="9">
         <v>0</v>
       </c>
-      <c r="H28" s="47"/>
+      <c r="H28" s="40"/>
       <c r="I28" s="13" t="s">
         <v>35</v>
       </c>
@@ -4465,7 +4471,7 @@
       <c r="G29" s="9">
         <v>0</v>
       </c>
-      <c r="H29" s="47"/>
+      <c r="H29" s="40"/>
       <c r="I29" s="13"/>
       <c r="J29" s="14"/>
     </row>
@@ -4491,7 +4497,7 @@
       <c r="G30" s="9">
         <v>0</v>
       </c>
-      <c r="H30" s="47"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="13"/>
       <c r="J30" s="14"/>
       <c r="K30" s="1"/>
@@ -4522,7 +4528,7 @@
       <c r="G31" s="9">
         <v>0</v>
       </c>
-      <c r="H31" s="47"/>
+      <c r="H31" s="40"/>
       <c r="I31" s="13"/>
       <c r="J31" s="14"/>
     </row>
@@ -4548,7 +4554,7 @@
       <c r="G32" s="9">
         <v>0</v>
       </c>
-      <c r="H32" s="47"/>
+      <c r="H32" s="40"/>
       <c r="I32" s="13"/>
       <c r="J32" s="14"/>
     </row>
@@ -4574,7 +4580,7 @@
       <c r="G33" s="9">
         <v>0</v>
       </c>
-      <c r="H33" s="47"/>
+      <c r="H33" s="40"/>
       <c r="I33" s="13"/>
       <c r="J33" s="14"/>
     </row>
@@ -4600,7 +4606,7 @@
       <c r="G34" s="9">
         <v>0</v>
       </c>
-      <c r="H34" s="47"/>
+      <c r="H34" s="40"/>
       <c r="I34" s="13"/>
       <c r="J34" s="14"/>
     </row>
@@ -4626,7 +4632,7 @@
       <c r="G35" s="9">
         <v>0</v>
       </c>
-      <c r="H35" s="47"/>
+      <c r="H35" s="40"/>
       <c r="I35" s="13"/>
       <c r="J35" s="14"/>
     </row>
@@ -4652,7 +4658,7 @@
       <c r="G36" s="9">
         <v>0</v>
       </c>
-      <c r="H36" s="47"/>
+      <c r="H36" s="40"/>
       <c r="I36" s="13"/>
       <c r="J36" s="14"/>
     </row>
@@ -4678,7 +4684,7 @@
       <c r="G37" s="9">
         <v>0</v>
       </c>
-      <c r="H37" s="47"/>
+      <c r="H37" s="40"/>
       <c r="I37" s="13"/>
       <c r="J37" s="14"/>
     </row>
@@ -4704,7 +4710,7 @@
       <c r="G38" s="9">
         <v>0</v>
       </c>
-      <c r="H38" s="47"/>
+      <c r="H38" s="40"/>
       <c r="I38" s="13"/>
       <c r="J38" s="14"/>
     </row>
@@ -4730,7 +4736,7 @@
       <c r="G39" s="9">
         <v>0</v>
       </c>
-      <c r="H39" s="47"/>
+      <c r="H39" s="40"/>
       <c r="I39" s="13"/>
       <c r="J39" s="14"/>
     </row>
@@ -4756,7 +4762,7 @@
       <c r="G40" s="9">
         <v>0</v>
       </c>
-      <c r="H40" s="47"/>
+      <c r="H40" s="40"/>
       <c r="I40" s="13" t="s">
         <v>48</v>
       </c>
@@ -4786,7 +4792,7 @@
       <c r="G41" s="9">
         <v>0</v>
       </c>
-      <c r="H41" s="47"/>
+      <c r="H41" s="40"/>
       <c r="I41" s="13"/>
       <c r="J41" s="14" t="s">
         <v>782</v>
@@ -4814,7 +4820,7 @@
       <c r="G42" s="9">
         <v>0</v>
       </c>
-      <c r="H42" s="47"/>
+      <c r="H42" s="40"/>
       <c r="I42" s="13"/>
       <c r="J42" s="14"/>
     </row>
@@ -4840,7 +4846,7 @@
       <c r="G43" s="9">
         <v>0</v>
       </c>
-      <c r="H43" s="47"/>
+      <c r="H43" s="40"/>
       <c r="I43" s="13"/>
       <c r="J43" s="14"/>
     </row>
@@ -4866,7 +4872,7 @@
       <c r="G44" s="9">
         <v>0</v>
       </c>
-      <c r="H44" s="47"/>
+      <c r="H44" s="40"/>
       <c r="I44" s="13"/>
       <c r="J44" s="14"/>
     </row>
@@ -4892,7 +4898,7 @@
       <c r="G45" s="9">
         <v>0</v>
       </c>
-      <c r="H45" s="47"/>
+      <c r="H45" s="40"/>
       <c r="I45" s="13"/>
       <c r="J45" s="14"/>
     </row>
@@ -4918,7 +4924,7 @@
       <c r="G46" s="9">
         <v>0</v>
       </c>
-      <c r="H46" s="47"/>
+      <c r="H46" s="40"/>
       <c r="I46" s="13"/>
       <c r="J46" s="14"/>
     </row>
@@ -4944,7 +4950,7 @@
       <c r="G47" s="9">
         <v>0</v>
       </c>
-      <c r="H47" s="47"/>
+      <c r="H47" s="40"/>
       <c r="I47" s="13"/>
       <c r="J47" s="14" t="s">
         <v>783</v>
@@ -4972,7 +4978,7 @@
       <c r="G48" s="9">
         <v>0</v>
       </c>
-      <c r="H48" s="47"/>
+      <c r="H48" s="40"/>
       <c r="I48" s="13"/>
       <c r="J48" s="14"/>
     </row>
@@ -4998,7 +5004,7 @@
       <c r="G49" s="9">
         <v>0</v>
       </c>
-      <c r="H49" s="47"/>
+      <c r="H49" s="40"/>
       <c r="I49" s="13"/>
       <c r="J49" s="14"/>
     </row>
@@ -5024,7 +5030,7 @@
       <c r="G50" s="9">
         <v>0</v>
       </c>
-      <c r="H50" s="47"/>
+      <c r="H50" s="40"/>
       <c r="I50" s="13"/>
       <c r="J50" s="14" t="s">
         <v>784</v>
@@ -5052,7 +5058,7 @@
       <c r="G51" s="9">
         <v>0</v>
       </c>
-      <c r="H51" s="47"/>
+      <c r="H51" s="40"/>
       <c r="I51" s="13" t="s">
         <v>60</v>
       </c>
@@ -5082,7 +5088,7 @@
       <c r="G52" s="9">
         <v>0</v>
       </c>
-      <c r="H52" s="47"/>
+      <c r="H52" s="40"/>
       <c r="I52" s="13" t="s">
         <v>62</v>
       </c>
@@ -5110,7 +5116,7 @@
       <c r="G53" s="9">
         <v>0</v>
       </c>
-      <c r="H53" s="47"/>
+      <c r="H53" s="40"/>
       <c r="I53" s="13" t="s">
         <v>64</v>
       </c>
@@ -5140,7 +5146,7 @@
       <c r="G54" s="9">
         <v>0</v>
       </c>
-      <c r="H54" s="47"/>
+      <c r="H54" s="40"/>
       <c r="I54" s="13" t="s">
         <v>66</v>
       </c>
@@ -5168,7 +5174,7 @@
       <c r="G55" s="9">
         <v>0</v>
       </c>
-      <c r="H55" s="47"/>
+      <c r="H55" s="40"/>
       <c r="I55" s="13"/>
       <c r="J55" s="14" t="s">
         <v>787</v>
@@ -5196,7 +5202,7 @@
       <c r="G56" s="9">
         <v>0</v>
       </c>
-      <c r="H56" s="47"/>
+      <c r="H56" s="40"/>
       <c r="I56" s="13"/>
       <c r="J56" s="14"/>
     </row>
@@ -5222,7 +5228,7 @@
       <c r="G57" s="9">
         <v>0</v>
       </c>
-      <c r="H57" s="47"/>
+      <c r="H57" s="40"/>
       <c r="I57" s="13"/>
       <c r="J57" s="14"/>
     </row>
@@ -5248,7 +5254,7 @@
       <c r="G58" s="9">
         <v>0</v>
       </c>
-      <c r="H58" s="47"/>
+      <c r="H58" s="40"/>
       <c r="I58" s="13" t="s">
         <v>71</v>
       </c>
@@ -5278,7 +5284,7 @@
       <c r="G59" s="9">
         <v>0</v>
       </c>
-      <c r="H59" s="47"/>
+      <c r="H59" s="40"/>
       <c r="I59" s="13"/>
       <c r="J59" s="14"/>
     </row>
@@ -5304,7 +5310,7 @@
       <c r="G60" s="9">
         <v>0</v>
       </c>
-      <c r="H60" s="47"/>
+      <c r="H60" s="40"/>
       <c r="I60" s="13"/>
       <c r="J60" s="14"/>
     </row>
@@ -5330,7 +5336,7 @@
       <c r="G61" s="9">
         <v>0</v>
       </c>
-      <c r="H61" s="47"/>
+      <c r="H61" s="40"/>
       <c r="I61" s="13" t="s">
         <v>75</v>
       </c>
@@ -5360,7 +5366,7 @@
       <c r="G62" s="9">
         <v>0</v>
       </c>
-      <c r="H62" s="47"/>
+      <c r="H62" s="40"/>
       <c r="I62" s="13" t="s">
         <v>77</v>
       </c>
@@ -5390,7 +5396,7 @@
       <c r="G63" s="9">
         <v>0</v>
       </c>
-      <c r="H63" s="47"/>
+      <c r="H63" s="40"/>
       <c r="I63" s="13" t="s">
         <v>80</v>
       </c>
@@ -5420,7 +5426,7 @@
       <c r="G64" s="9">
         <v>0</v>
       </c>
-      <c r="H64" s="47"/>
+      <c r="H64" s="40"/>
       <c r="I64" s="13"/>
       <c r="J64" s="14"/>
     </row>
@@ -5446,7 +5452,7 @@
       <c r="G65" s="9">
         <v>0</v>
       </c>
-      <c r="H65" s="47"/>
+      <c r="H65" s="40"/>
       <c r="I65" s="13"/>
       <c r="J65" s="14"/>
     </row>
@@ -5472,7 +5478,7 @@
       <c r="G66" s="9">
         <v>0</v>
       </c>
-      <c r="H66" s="47"/>
+      <c r="H66" s="40"/>
       <c r="I66" s="13"/>
       <c r="J66" s="14"/>
     </row>
@@ -5498,7 +5504,7 @@
       <c r="G67" s="9">
         <v>0</v>
       </c>
-      <c r="H67" s="47"/>
+      <c r="H67" s="40"/>
       <c r="I67" s="13"/>
       <c r="J67" s="14"/>
     </row>
@@ -5524,7 +5530,7 @@
       <c r="G68" s="9">
         <v>0</v>
       </c>
-      <c r="H68" s="47"/>
+      <c r="H68" s="40"/>
       <c r="I68" s="13"/>
       <c r="J68" s="14"/>
     </row>
@@ -5550,7 +5556,7 @@
       <c r="G69" s="9">
         <v>0</v>
       </c>
-      <c r="H69" s="47"/>
+      <c r="H69" s="40"/>
       <c r="I69" s="13"/>
       <c r="J69" s="14"/>
     </row>
@@ -5576,7 +5582,7 @@
       <c r="G70" s="9">
         <v>0</v>
       </c>
-      <c r="H70" s="47"/>
+      <c r="H70" s="40"/>
       <c r="I70" s="13" t="s">
         <v>88</v>
       </c>
@@ -5606,7 +5612,7 @@
       <c r="G71" s="9">
         <v>0</v>
       </c>
-      <c r="H71" s="47"/>
+      <c r="H71" s="40"/>
       <c r="I71" s="13" t="s">
         <v>90</v>
       </c>
@@ -5634,7 +5640,7 @@
       <c r="G72" s="9">
         <v>0</v>
       </c>
-      <c r="H72" s="47"/>
+      <c r="H72" s="40"/>
       <c r="I72" s="13"/>
       <c r="J72" s="14"/>
     </row>
@@ -5660,7 +5666,7 @@
       <c r="G73" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="H73" s="47"/>
+      <c r="H73" s="40"/>
       <c r="I73" s="13"/>
       <c r="J73" s="14"/>
     </row>
@@ -5686,7 +5692,7 @@
       <c r="G74" s="9">
         <v>0</v>
       </c>
-      <c r="H74" s="47"/>
+      <c r="H74" s="40"/>
       <c r="I74" s="13"/>
       <c r="J74" s="14"/>
     </row>
@@ -5712,7 +5718,7 @@
       <c r="G75" s="9">
         <v>0</v>
       </c>
-      <c r="H75" s="47"/>
+      <c r="H75" s="40"/>
       <c r="I75" s="13"/>
       <c r="J75" s="14"/>
     </row>
@@ -5738,7 +5744,7 @@
       <c r="G76" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="H76" s="47"/>
+      <c r="H76" s="40"/>
       <c r="I76" s="13"/>
       <c r="J76" s="14"/>
     </row>
@@ -5764,7 +5770,7 @@
       <c r="G77" s="9">
         <v>0</v>
       </c>
-      <c r="H77" s="47"/>
+      <c r="H77" s="40"/>
       <c r="I77" s="13"/>
       <c r="J77" s="14"/>
     </row>
@@ -5790,7 +5796,7 @@
       <c r="G78" s="9">
         <v>0</v>
       </c>
-      <c r="H78" s="47"/>
+      <c r="H78" s="40"/>
       <c r="I78" s="13" t="s">
         <v>98</v>
       </c>
@@ -5820,7 +5826,7 @@
       <c r="G79" s="9" t="s">
         <v>592</v>
       </c>
-      <c r="H79" s="47"/>
+      <c r="H79" s="40"/>
       <c r="I79" s="13"/>
       <c r="J79" s="14"/>
     </row>
@@ -5846,7 +5852,7 @@
       <c r="G80" s="9">
         <v>0</v>
       </c>
-      <c r="H80" s="47"/>
+      <c r="H80" s="40"/>
       <c r="I80" s="13"/>
       <c r="J80" s="14"/>
     </row>
@@ -5872,7 +5878,7 @@
       <c r="G81" s="9">
         <v>0</v>
       </c>
-      <c r="H81" s="47"/>
+      <c r="H81" s="40"/>
       <c r="I81" s="13"/>
       <c r="J81" s="14"/>
     </row>
@@ -5898,7 +5904,7 @@
       <c r="G82" s="9">
         <v>0</v>
       </c>
-      <c r="H82" s="47"/>
+      <c r="H82" s="40"/>
       <c r="I82" s="13"/>
       <c r="J82" s="14"/>
     </row>
@@ -5924,7 +5930,7 @@
       <c r="G83" s="9">
         <v>0</v>
       </c>
-      <c r="H83" s="47"/>
+      <c r="H83" s="40"/>
       <c r="I83" s="13"/>
       <c r="J83" s="14"/>
     </row>
@@ -5950,7 +5956,7 @@
       <c r="G84" s="9">
         <v>0</v>
       </c>
-      <c r="H84" s="47"/>
+      <c r="H84" s="40"/>
       <c r="I84" s="13"/>
       <c r="J84" s="14"/>
     </row>
@@ -5976,7 +5982,7 @@
       <c r="G85" s="9">
         <v>0</v>
       </c>
-      <c r="H85" s="47"/>
+      <c r="H85" s="40"/>
       <c r="I85" s="13"/>
       <c r="J85" s="14"/>
     </row>
@@ -6002,7 +6008,7 @@
       <c r="G86" s="9">
         <v>0</v>
       </c>
-      <c r="H86" s="47"/>
+      <c r="H86" s="40"/>
       <c r="I86" s="13"/>
       <c r="J86" s="14" t="s">
         <v>794</v>
@@ -6030,7 +6036,7 @@
       <c r="G87" s="9">
         <v>0</v>
       </c>
-      <c r="H87" s="47"/>
+      <c r="H87" s="40"/>
       <c r="I87" s="13"/>
       <c r="J87" s="14"/>
     </row>
@@ -6056,7 +6062,7 @@
       <c r="G88" s="9">
         <v>0</v>
       </c>
-      <c r="H88" s="47"/>
+      <c r="H88" s="40"/>
       <c r="I88" s="13"/>
       <c r="J88" s="14"/>
     </row>
@@ -6082,7 +6088,7 @@
       <c r="G89" s="9">
         <v>0</v>
       </c>
-      <c r="H89" s="47"/>
+      <c r="H89" s="40"/>
       <c r="I89" s="13"/>
       <c r="J89" s="14"/>
     </row>
@@ -6108,7 +6114,7 @@
       <c r="G90" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="H90" s="47"/>
+      <c r="H90" s="40"/>
       <c r="I90" s="13"/>
       <c r="J90" s="14"/>
     </row>
@@ -6134,7 +6140,7 @@
       <c r="G91" s="9">
         <v>0</v>
       </c>
-      <c r="H91" s="47"/>
+      <c r="H91" s="40"/>
       <c r="I91" s="13" t="s">
         <v>112</v>
       </c>
@@ -6162,7 +6168,7 @@
       <c r="G92" s="9">
         <v>0</v>
       </c>
-      <c r="H92" s="47"/>
+      <c r="H92" s="40"/>
       <c r="I92" s="13" t="s">
         <v>114</v>
       </c>
@@ -6192,7 +6198,7 @@
       <c r="G93" s="9">
         <v>0</v>
       </c>
-      <c r="H93" s="47"/>
+      <c r="H93" s="40"/>
       <c r="I93" s="13" t="s">
         <v>117</v>
       </c>
@@ -6222,7 +6228,7 @@
       <c r="G94" s="9">
         <v>0</v>
       </c>
-      <c r="H94" s="47"/>
+      <c r="H94" s="40"/>
       <c r="I94" s="13"/>
       <c r="J94" s="14"/>
     </row>
@@ -6248,7 +6254,7 @@
       <c r="G95" s="9">
         <v>0</v>
       </c>
-      <c r="H95" s="47"/>
+      <c r="H95" s="40"/>
       <c r="I95" s="13"/>
       <c r="J95" s="14"/>
     </row>
@@ -6274,7 +6280,7 @@
       <c r="G96" s="9">
         <v>0</v>
       </c>
-      <c r="H96" s="47"/>
+      <c r="H96" s="40"/>
       <c r="I96" s="13"/>
       <c r="J96" s="14"/>
     </row>
@@ -6300,7 +6306,7 @@
       <c r="G97" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="H97" s="47"/>
+      <c r="H97" s="40"/>
       <c r="I97" s="13"/>
       <c r="J97" s="14"/>
     </row>
@@ -6326,7 +6332,7 @@
       <c r="G98" s="9">
         <v>0</v>
       </c>
-      <c r="H98" s="47"/>
+      <c r="H98" s="40"/>
       <c r="I98" s="13"/>
       <c r="J98" s="14"/>
     </row>
@@ -6352,7 +6358,7 @@
       <c r="G99" s="9">
         <v>0</v>
       </c>
-      <c r="H99" s="47"/>
+      <c r="H99" s="40"/>
       <c r="I99" s="13"/>
       <c r="J99" s="14"/>
     </row>
@@ -6378,7 +6384,7 @@
       <c r="G100" s="9">
         <v>0</v>
       </c>
-      <c r="H100" s="47"/>
+      <c r="H100" s="40"/>
       <c r="I100" s="13"/>
       <c r="J100" s="14"/>
     </row>
@@ -6404,7 +6410,7 @@
       <c r="G101" s="9">
         <v>0</v>
       </c>
-      <c r="H101" s="47"/>
+      <c r="H101" s="40"/>
       <c r="I101" s="13"/>
       <c r="J101" s="14"/>
     </row>
@@ -6430,7 +6436,7 @@
       <c r="G102" s="9">
         <v>0</v>
       </c>
-      <c r="H102" s="47"/>
+      <c r="H102" s="40"/>
       <c r="I102" s="13"/>
       <c r="J102" s="14"/>
     </row>
@@ -6456,7 +6462,7 @@
       <c r="G103" s="9">
         <v>0</v>
       </c>
-      <c r="H103" s="47"/>
+      <c r="H103" s="40"/>
       <c r="I103" s="13"/>
       <c r="J103" s="14"/>
     </row>
@@ -6482,7 +6488,7 @@
       <c r="G104" s="9">
         <v>0</v>
       </c>
-      <c r="H104" s="47"/>
+      <c r="H104" s="40"/>
       <c r="I104" s="13"/>
       <c r="J104" s="14"/>
     </row>
@@ -6508,7 +6514,7 @@
       <c r="G105" s="9">
         <v>0</v>
       </c>
-      <c r="H105" s="47"/>
+      <c r="H105" s="40"/>
       <c r="I105" s="13"/>
       <c r="J105" s="14"/>
     </row>
@@ -6534,7 +6540,7 @@
       <c r="G106" s="9">
         <v>0</v>
       </c>
-      <c r="H106" s="47"/>
+      <c r="H106" s="40"/>
       <c r="I106" s="13"/>
       <c r="J106" s="14"/>
     </row>
@@ -6560,7 +6566,7 @@
       <c r="G107" s="9">
         <v>0</v>
       </c>
-      <c r="H107" s="47"/>
+      <c r="H107" s="40"/>
       <c r="I107" s="13"/>
       <c r="J107" s="14"/>
     </row>
@@ -6586,7 +6592,7 @@
       <c r="G108" s="9">
         <v>0</v>
       </c>
-      <c r="H108" s="47"/>
+      <c r="H108" s="40"/>
       <c r="I108" s="13"/>
       <c r="J108" s="14"/>
     </row>
@@ -6612,7 +6618,7 @@
       <c r="G109" s="9">
         <v>0</v>
       </c>
-      <c r="H109" s="47"/>
+      <c r="H109" s="40"/>
       <c r="I109" s="13"/>
       <c r="J109" s="14"/>
     </row>
@@ -6638,7 +6644,7 @@
       <c r="G110" s="9">
         <v>0</v>
       </c>
-      <c r="H110" s="47"/>
+      <c r="H110" s="40"/>
       <c r="I110" s="13"/>
       <c r="J110" s="14"/>
     </row>
@@ -6664,7 +6670,7 @@
       <c r="G111" s="9">
         <v>0</v>
       </c>
-      <c r="H111" s="47"/>
+      <c r="H111" s="40"/>
       <c r="I111" s="13"/>
       <c r="J111" s="14"/>
     </row>
@@ -6690,7 +6696,7 @@
       <c r="G112" s="9">
         <v>0</v>
       </c>
-      <c r="H112" s="47"/>
+      <c r="H112" s="40"/>
       <c r="I112" s="13"/>
       <c r="J112" s="14"/>
     </row>
@@ -6716,7 +6722,7 @@
       <c r="G113" s="9">
         <v>0</v>
       </c>
-      <c r="H113" s="47"/>
+      <c r="H113" s="40"/>
       <c r="I113" s="13"/>
       <c r="J113" s="14"/>
     </row>
@@ -6742,7 +6748,7 @@
       <c r="G114" s="9">
         <v>0</v>
       </c>
-      <c r="H114" s="47"/>
+      <c r="H114" s="40"/>
       <c r="I114" s="13" t="s">
         <v>140</v>
       </c>
@@ -6770,7 +6776,7 @@
       <c r="G115" s="9">
         <v>0</v>
       </c>
-      <c r="H115" s="47"/>
+      <c r="H115" s="40"/>
       <c r="I115" s="13"/>
       <c r="J115" s="14"/>
     </row>
@@ -6796,7 +6802,7 @@
       <c r="G116" s="9">
         <v>0</v>
       </c>
-      <c r="H116" s="47"/>
+      <c r="H116" s="40"/>
       <c r="I116" s="13"/>
       <c r="J116" s="14"/>
     </row>
@@ -6822,7 +6828,7 @@
       <c r="G117" s="9">
         <v>0</v>
       </c>
-      <c r="H117" s="47"/>
+      <c r="H117" s="40"/>
       <c r="I117" s="13"/>
       <c r="J117" s="14"/>
     </row>
@@ -6848,7 +6854,7 @@
       <c r="G118" s="9">
         <v>0</v>
       </c>
-      <c r="H118" s="47"/>
+      <c r="H118" s="40"/>
       <c r="I118" s="13"/>
       <c r="J118" s="14"/>
     </row>
@@ -6874,7 +6880,7 @@
       <c r="G119" s="9">
         <v>0</v>
       </c>
-      <c r="H119" s="47"/>
+      <c r="H119" s="40"/>
       <c r="I119" s="13"/>
       <c r="J119" s="14" t="s">
         <v>796</v>
@@ -6902,7 +6908,7 @@
       <c r="G120" s="9">
         <v>0</v>
       </c>
-      <c r="H120" s="47"/>
+      <c r="H120" s="40"/>
       <c r="I120" s="13"/>
       <c r="J120" s="14"/>
     </row>
@@ -6928,7 +6934,7 @@
       <c r="G121" s="9">
         <v>0</v>
       </c>
-      <c r="H121" s="47"/>
+      <c r="H121" s="40"/>
       <c r="I121" s="13"/>
       <c r="J121" s="14"/>
     </row>
@@ -6954,7 +6960,7 @@
       <c r="G122" s="9">
         <v>0</v>
       </c>
-      <c r="H122" s="47"/>
+      <c r="H122" s="40"/>
       <c r="I122" s="13" t="s">
         <v>149</v>
       </c>
@@ -6984,7 +6990,7 @@
       <c r="G123" s="9">
         <v>0</v>
       </c>
-      <c r="H123" s="47"/>
+      <c r="H123" s="40"/>
       <c r="I123" s="13"/>
       <c r="J123" s="14"/>
     </row>
@@ -7010,7 +7016,7 @@
       <c r="G124" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="H124" s="47"/>
+      <c r="H124" s="40"/>
       <c r="I124" s="13"/>
       <c r="J124" s="14"/>
     </row>
@@ -7036,7 +7042,7 @@
       <c r="G125" s="9">
         <v>0</v>
       </c>
-      <c r="H125" s="47"/>
+      <c r="H125" s="40"/>
       <c r="I125" s="13"/>
       <c r="J125" s="14"/>
     </row>
@@ -7062,7 +7068,7 @@
       <c r="G126" s="9">
         <v>0</v>
       </c>
-      <c r="H126" s="47"/>
+      <c r="H126" s="40"/>
       <c r="I126" s="13"/>
       <c r="J126" s="14"/>
     </row>
@@ -7088,7 +7094,7 @@
       <c r="G127" s="9">
         <v>0</v>
       </c>
-      <c r="H127" s="47"/>
+      <c r="H127" s="40"/>
       <c r="I127" s="13"/>
       <c r="J127" s="14"/>
     </row>
@@ -7114,7 +7120,7 @@
       <c r="G128" s="9">
         <v>0</v>
       </c>
-      <c r="H128" s="47"/>
+      <c r="H128" s="40"/>
       <c r="I128" s="13"/>
       <c r="J128" s="14"/>
     </row>
@@ -7140,7 +7146,7 @@
       <c r="G129" s="9">
         <v>0</v>
       </c>
-      <c r="H129" s="47"/>
+      <c r="H129" s="40"/>
       <c r="I129" s="13"/>
       <c r="J129" s="14"/>
     </row>
@@ -7166,7 +7172,7 @@
       <c r="G130" s="9">
         <v>0</v>
       </c>
-      <c r="H130" s="47"/>
+      <c r="H130" s="40"/>
       <c r="I130" s="13"/>
       <c r="J130" s="14"/>
     </row>
@@ -7192,7 +7198,7 @@
       <c r="G131" s="9">
         <v>0</v>
       </c>
-      <c r="H131" s="47"/>
+      <c r="H131" s="40"/>
       <c r="I131" s="13"/>
       <c r="J131" s="14"/>
     </row>
@@ -7218,7 +7224,7 @@
       <c r="G132" s="9">
         <v>0</v>
       </c>
-      <c r="H132" s="47"/>
+      <c r="H132" s="40"/>
       <c r="I132" s="13"/>
       <c r="J132" s="14"/>
     </row>
@@ -7244,7 +7250,7 @@
       <c r="G133" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="H133" s="47"/>
+      <c r="H133" s="40"/>
       <c r="I133" s="13"/>
       <c r="J133" s="14"/>
     </row>
@@ -7270,7 +7276,7 @@
       <c r="G134" s="9">
         <v>0</v>
       </c>
-      <c r="H134" s="47"/>
+      <c r="H134" s="40"/>
       <c r="I134" s="13" t="s">
         <v>162</v>
       </c>
@@ -7300,7 +7306,7 @@
       <c r="G135" s="9">
         <v>0</v>
       </c>
-      <c r="H135" s="47"/>
+      <c r="H135" s="40"/>
       <c r="I135" s="13"/>
       <c r="J135" s="14"/>
     </row>
@@ -7326,7 +7332,7 @@
       <c r="G136" s="9">
         <v>0</v>
       </c>
-      <c r="H136" s="47"/>
+      <c r="H136" s="40"/>
       <c r="I136" s="13" t="s">
         <v>165</v>
       </c>
@@ -7356,7 +7362,7 @@
       <c r="G137" s="9">
         <v>0</v>
       </c>
-      <c r="H137" s="47"/>
+      <c r="H137" s="40"/>
       <c r="I137" s="13"/>
       <c r="J137" s="14" t="s">
         <v>800</v>
@@ -7384,7 +7390,7 @@
       <c r="G138" s="9">
         <v>0</v>
       </c>
-      <c r="H138" s="47"/>
+      <c r="H138" s="40"/>
       <c r="I138" s="13"/>
       <c r="J138" s="14"/>
     </row>
@@ -7410,7 +7416,7 @@
       <c r="G139" s="9">
         <v>0</v>
       </c>
-      <c r="H139" s="47"/>
+      <c r="H139" s="40"/>
       <c r="I139" s="13"/>
       <c r="J139" s="14"/>
     </row>
@@ -7436,7 +7442,7 @@
       <c r="G140" s="9">
         <v>0</v>
       </c>
-      <c r="H140" s="47"/>
+      <c r="H140" s="40"/>
       <c r="I140" s="13"/>
       <c r="J140" s="14"/>
     </row>
@@ -7462,7 +7468,7 @@
       <c r="G141" s="9">
         <v>0</v>
       </c>
-      <c r="H141" s="47"/>
+      <c r="H141" s="40"/>
       <c r="I141" s="13"/>
       <c r="J141" s="14"/>
     </row>
@@ -7488,7 +7494,7 @@
       <c r="G142" s="9">
         <v>0</v>
       </c>
-      <c r="H142" s="47"/>
+      <c r="H142" s="40"/>
       <c r="I142" s="13"/>
       <c r="J142" s="14"/>
     </row>
@@ -7514,7 +7520,7 @@
       <c r="G143" s="9">
         <v>0</v>
       </c>
-      <c r="H143" s="47"/>
+      <c r="H143" s="40"/>
       <c r="I143" s="13"/>
       <c r="J143" s="14"/>
     </row>
@@ -7540,7 +7546,7 @@
       <c r="G144" s="9">
         <v>0</v>
       </c>
-      <c r="H144" s="47"/>
+      <c r="H144" s="40"/>
       <c r="I144" s="13"/>
       <c r="J144" s="14"/>
     </row>
@@ -7566,7 +7572,7 @@
       <c r="G145" s="9">
         <v>0</v>
       </c>
-      <c r="H145" s="47"/>
+      <c r="H145" s="40"/>
       <c r="I145" s="13"/>
       <c r="J145" s="14"/>
     </row>
@@ -7592,7 +7598,7 @@
       <c r="G146" s="9">
         <v>0</v>
       </c>
-      <c r="H146" s="47"/>
+      <c r="H146" s="40"/>
       <c r="I146" s="13"/>
       <c r="J146" s="14"/>
     </row>
@@ -7618,7 +7624,7 @@
       <c r="G147" s="9">
         <v>0</v>
       </c>
-      <c r="H147" s="47"/>
+      <c r="H147" s="40"/>
       <c r="I147" s="13"/>
       <c r="J147" s="14" t="s">
         <v>801</v>
@@ -7646,7 +7652,7 @@
       <c r="G148" s="9">
         <v>0</v>
       </c>
-      <c r="H148" s="47"/>
+      <c r="H148" s="40"/>
       <c r="I148" s="13"/>
       <c r="J148" s="14"/>
     </row>
@@ -7672,7 +7678,7 @@
       <c r="G149" s="9">
         <v>0</v>
       </c>
-      <c r="H149" s="47"/>
+      <c r="H149" s="40"/>
       <c r="I149" s="13" t="s">
         <v>182</v>
       </c>
@@ -7702,7 +7708,7 @@
       <c r="G150" s="9">
         <v>0</v>
       </c>
-      <c r="H150" s="47"/>
+      <c r="H150" s="40"/>
       <c r="I150" s="13" t="s">
         <v>178</v>
       </c>
@@ -7730,7 +7736,7 @@
       <c r="G151" s="9">
         <v>0</v>
       </c>
-      <c r="H151" s="47"/>
+      <c r="H151" s="40"/>
       <c r="I151" s="13" t="s">
         <v>180</v>
       </c>
@@ -7760,7 +7766,7 @@
       <c r="G152" s="9">
         <v>0</v>
       </c>
-      <c r="H152" s="47"/>
+      <c r="H152" s="40"/>
       <c r="I152" s="13" t="s">
         <v>184</v>
       </c>
@@ -7790,7 +7796,7 @@
       <c r="G153" s="9">
         <v>0</v>
       </c>
-      <c r="H153" s="47"/>
+      <c r="H153" s="40"/>
       <c r="I153" s="13"/>
       <c r="J153" s="14"/>
     </row>
@@ -7816,7 +7822,7 @@
       <c r="G154" s="9">
         <v>0</v>
       </c>
-      <c r="H154" s="47"/>
+      <c r="H154" s="40"/>
       <c r="I154" s="13"/>
       <c r="J154" s="14"/>
     </row>
@@ -7842,7 +7848,7 @@
       <c r="G155" s="9">
         <v>0</v>
       </c>
-      <c r="H155" s="47"/>
+      <c r="H155" s="40"/>
       <c r="I155" s="13"/>
       <c r="J155" s="14"/>
     </row>
@@ -7868,7 +7874,7 @@
       <c r="G156" s="9">
         <v>0</v>
       </c>
-      <c r="H156" s="47"/>
+      <c r="H156" s="40"/>
       <c r="I156" s="13"/>
       <c r="J156" s="14"/>
     </row>
@@ -7894,7 +7900,7 @@
       <c r="G157" s="9">
         <v>0</v>
       </c>
-      <c r="H157" s="47"/>
+      <c r="H157" s="40"/>
       <c r="I157" s="13" t="s">
         <v>191</v>
       </c>
@@ -7924,7 +7930,7 @@
       <c r="G158" s="9">
         <v>0</v>
       </c>
-      <c r="H158" s="47"/>
+      <c r="H158" s="40"/>
       <c r="I158" s="13"/>
       <c r="J158" s="14"/>
     </row>
@@ -7950,7 +7956,7 @@
       <c r="G159" s="9">
         <v>0</v>
       </c>
-      <c r="H159" s="47"/>
+      <c r="H159" s="40"/>
       <c r="I159" s="13"/>
       <c r="J159" s="14" t="s">
         <v>806</v>
@@ -7978,7 +7984,7 @@
       <c r="G160" s="9">
         <v>0</v>
       </c>
-      <c r="H160" s="47"/>
+      <c r="H160" s="40"/>
       <c r="I160" s="13"/>
       <c r="J160" s="14" t="s">
         <v>806</v>
@@ -8006,7 +8012,7 @@
       <c r="G161" s="9">
         <v>0</v>
       </c>
-      <c r="H161" s="47"/>
+      <c r="H161" s="40"/>
       <c r="I161" s="13"/>
       <c r="J161" s="14"/>
     </row>
@@ -8032,7 +8038,7 @@
       <c r="G162" s="9">
         <v>0</v>
       </c>
-      <c r="H162" s="47"/>
+      <c r="H162" s="40"/>
       <c r="I162" s="13" t="s">
         <v>197</v>
       </c>
@@ -8062,7 +8068,7 @@
       <c r="G163" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="H163" s="47"/>
+      <c r="H163" s="40"/>
       <c r="I163" s="13"/>
       <c r="J163" s="14"/>
     </row>
@@ -8088,7 +8094,7 @@
       <c r="G164" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="H164" s="47"/>
+      <c r="H164" s="40"/>
       <c r="I164" s="13"/>
       <c r="J164" s="14"/>
     </row>
@@ -8114,7 +8120,7 @@
       <c r="G165" s="9">
         <v>0</v>
       </c>
-      <c r="H165" s="47"/>
+      <c r="H165" s="40"/>
       <c r="I165" s="13"/>
       <c r="J165" s="14"/>
     </row>
@@ -8140,7 +8146,7 @@
       <c r="G166" s="9">
         <v>0</v>
       </c>
-      <c r="H166" s="47"/>
+      <c r="H166" s="40"/>
       <c r="I166" s="13"/>
       <c r="J166" s="14"/>
     </row>
@@ -8166,7 +8172,7 @@
       <c r="G167" s="9">
         <v>0</v>
       </c>
-      <c r="H167" s="47"/>
+      <c r="H167" s="40"/>
       <c r="I167" s="13"/>
       <c r="J167" s="14"/>
     </row>
@@ -8192,7 +8198,7 @@
       <c r="G168" s="9">
         <v>0</v>
       </c>
-      <c r="H168" s="47"/>
+      <c r="H168" s="40"/>
       <c r="I168" s="13"/>
       <c r="J168" s="14"/>
     </row>
@@ -8218,7 +8224,7 @@
       <c r="G169" s="9">
         <v>0</v>
       </c>
-      <c r="H169" s="47"/>
+      <c r="H169" s="40"/>
       <c r="I169" s="13"/>
       <c r="J169" s="14"/>
     </row>
@@ -8244,7 +8250,7 @@
       <c r="G170" s="9">
         <v>0</v>
       </c>
-      <c r="H170" s="47"/>
+      <c r="H170" s="40"/>
       <c r="I170" s="13"/>
       <c r="J170" s="14"/>
     </row>
@@ -8270,7 +8276,7 @@
       <c r="G171" s="9">
         <v>0</v>
       </c>
-      <c r="H171" s="47"/>
+      <c r="H171" s="40"/>
       <c r="I171" s="13"/>
       <c r="J171" s="14"/>
     </row>
@@ -8296,7 +8302,7 @@
       <c r="G172" s="9">
         <v>0</v>
       </c>
-      <c r="H172" s="47"/>
+      <c r="H172" s="40"/>
       <c r="I172" s="13"/>
       <c r="J172" s="14"/>
     </row>
@@ -8322,7 +8328,7 @@
       <c r="G173" s="9">
         <v>0</v>
       </c>
-      <c r="H173" s="47"/>
+      <c r="H173" s="40"/>
       <c r="I173" s="13"/>
       <c r="J173" s="14"/>
     </row>
@@ -8348,7 +8354,7 @@
       <c r="G174" s="9">
         <v>0</v>
       </c>
-      <c r="H174" s="47"/>
+      <c r="H174" s="40"/>
       <c r="I174" s="13"/>
       <c r="J174" s="14" t="s">
         <v>808</v>
@@ -8376,7 +8382,7 @@
       <c r="G175" s="9">
         <v>0</v>
       </c>
-      <c r="H175" s="47"/>
+      <c r="H175" s="40"/>
       <c r="I175" s="13"/>
       <c r="J175" s="14"/>
     </row>
@@ -8402,7 +8408,7 @@
       <c r="G176" s="9">
         <v>0</v>
       </c>
-      <c r="H176" s="47"/>
+      <c r="H176" s="40"/>
       <c r="I176" s="13" t="s">
         <v>214</v>
       </c>
@@ -8432,7 +8438,7 @@
       <c r="G177" s="9">
         <v>0</v>
       </c>
-      <c r="H177" s="47"/>
+      <c r="H177" s="40"/>
       <c r="I177" s="13" t="s">
         <v>216</v>
       </c>
@@ -8462,7 +8468,7 @@
       <c r="G178" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="H178" s="47"/>
+      <c r="H178" s="40"/>
       <c r="I178" s="13"/>
       <c r="J178" s="14"/>
     </row>
@@ -8488,7 +8494,7 @@
       <c r="G179" s="9">
         <v>0</v>
       </c>
-      <c r="H179" s="47"/>
+      <c r="H179" s="40"/>
       <c r="I179" s="13"/>
       <c r="J179" s="14"/>
     </row>
@@ -8514,7 +8520,7 @@
       <c r="G180" s="9">
         <v>0</v>
       </c>
-      <c r="H180" s="47"/>
+      <c r="H180" s="40"/>
       <c r="I180" s="13"/>
       <c r="J180" s="14"/>
     </row>
@@ -8540,7 +8546,7 @@
       <c r="G181" s="9">
         <v>0</v>
       </c>
-      <c r="H181" s="47"/>
+      <c r="H181" s="40"/>
       <c r="I181" s="13"/>
       <c r="J181" s="14"/>
     </row>
@@ -8566,7 +8572,7 @@
       <c r="G182" s="9">
         <v>0</v>
       </c>
-      <c r="H182" s="47"/>
+      <c r="H182" s="40"/>
       <c r="I182" s="13"/>
       <c r="J182" s="14"/>
     </row>
@@ -8592,7 +8598,7 @@
       <c r="G183" s="9">
         <v>0</v>
       </c>
-      <c r="H183" s="47"/>
+      <c r="H183" s="40"/>
       <c r="I183" s="13"/>
       <c r="J183" s="14"/>
     </row>
@@ -8618,7 +8624,7 @@
       <c r="G184" s="9">
         <v>0</v>
       </c>
-      <c r="H184" s="47"/>
+      <c r="H184" s="40"/>
       <c r="I184" s="13"/>
       <c r="J184" s="14"/>
     </row>
@@ -8644,7 +8650,7 @@
       <c r="G185" s="9">
         <v>0</v>
       </c>
-      <c r="H185" s="47"/>
+      <c r="H185" s="40"/>
       <c r="I185" s="13"/>
       <c r="J185" s="14"/>
     </row>
@@ -8670,7 +8676,7 @@
       <c r="G186" s="9">
         <v>0</v>
       </c>
-      <c r="H186" s="47"/>
+      <c r="H186" s="40"/>
       <c r="I186" s="13"/>
       <c r="J186" s="14"/>
     </row>
@@ -8696,7 +8702,7 @@
       <c r="G187" s="9">
         <v>0</v>
       </c>
-      <c r="H187" s="47"/>
+      <c r="H187" s="40"/>
       <c r="I187" s="13"/>
       <c r="J187" s="14"/>
     </row>
@@ -8722,7 +8728,7 @@
       <c r="G188" s="9">
         <v>0</v>
       </c>
-      <c r="H188" s="47"/>
+      <c r="H188" s="40"/>
       <c r="I188" s="13"/>
       <c r="J188" s="14"/>
     </row>
@@ -8748,7 +8754,7 @@
       <c r="G189" s="9">
         <v>0</v>
       </c>
-      <c r="H189" s="47"/>
+      <c r="H189" s="40"/>
       <c r="I189" s="13"/>
       <c r="J189" s="14"/>
     </row>
@@ -8774,7 +8780,7 @@
       <c r="G190" s="9">
         <v>0</v>
       </c>
-      <c r="H190" s="47"/>
+      <c r="H190" s="40"/>
       <c r="I190" s="13"/>
       <c r="J190" s="14"/>
     </row>
@@ -8800,7 +8806,7 @@
       <c r="G191" s="9">
         <v>0</v>
       </c>
-      <c r="H191" s="47"/>
+      <c r="H191" s="40"/>
       <c r="I191" s="13"/>
       <c r="J191" s="14"/>
     </row>
@@ -8826,7 +8832,7 @@
       <c r="G192" s="9">
         <v>0</v>
       </c>
-      <c r="H192" s="47"/>
+      <c r="H192" s="40"/>
       <c r="I192" s="13"/>
       <c r="J192" s="14"/>
     </row>
@@ -8852,7 +8858,7 @@
       <c r="G193" s="9">
         <v>0</v>
       </c>
-      <c r="H193" s="47"/>
+      <c r="H193" s="40"/>
       <c r="I193" s="13"/>
       <c r="J193" s="14"/>
     </row>
@@ -8878,7 +8884,7 @@
       <c r="G194" s="9">
         <v>0</v>
       </c>
-      <c r="H194" s="47"/>
+      <c r="H194" s="40"/>
       <c r="I194" s="13"/>
       <c r="J194" s="14"/>
     </row>
@@ -8904,7 +8910,7 @@
       <c r="G195" s="9">
         <v>0</v>
       </c>
-      <c r="H195" s="47"/>
+      <c r="H195" s="40"/>
       <c r="I195" s="13" t="s">
         <v>236</v>
       </c>
@@ -8934,7 +8940,7 @@
       <c r="G196" s="9">
         <v>0</v>
       </c>
-      <c r="H196" s="47"/>
+      <c r="H196" s="40"/>
       <c r="I196" s="13"/>
       <c r="J196" s="14"/>
     </row>
@@ -8960,7 +8966,7 @@
       <c r="G197" s="9">
         <v>0</v>
       </c>
-      <c r="H197" s="47"/>
+      <c r="H197" s="40"/>
       <c r="I197" s="13"/>
       <c r="J197" s="14"/>
     </row>
@@ -8986,7 +8992,7 @@
       <c r="G198" s="9">
         <v>0</v>
       </c>
-      <c r="H198" s="47"/>
+      <c r="H198" s="40"/>
       <c r="I198" s="13" t="s">
         <v>239</v>
       </c>
@@ -9016,7 +9022,7 @@
       <c r="G199" s="9">
         <v>0</v>
       </c>
-      <c r="H199" s="47"/>
+      <c r="H199" s="40"/>
       <c r="I199" s="13" t="s">
         <v>241</v>
       </c>
@@ -9046,7 +9052,7 @@
       <c r="G200" s="9">
         <v>0</v>
       </c>
-      <c r="H200" s="47"/>
+      <c r="H200" s="40"/>
       <c r="I200" s="13"/>
       <c r="J200" s="14"/>
     </row>
@@ -9072,7 +9078,7 @@
       <c r="G201" s="9">
         <v>0</v>
       </c>
-      <c r="H201" s="47"/>
+      <c r="H201" s="40"/>
       <c r="I201" s="13" t="s">
         <v>245</v>
       </c>
@@ -9100,7 +9106,7 @@
       <c r="G202" s="9">
         <v>0</v>
       </c>
-      <c r="H202" s="47"/>
+      <c r="H202" s="40"/>
       <c r="I202" s="13"/>
       <c r="J202" s="14" t="s">
         <v>815</v>
@@ -9128,7 +9134,7 @@
       <c r="G203" s="9">
         <v>0</v>
       </c>
-      <c r="H203" s="47"/>
+      <c r="H203" s="40"/>
       <c r="I203" s="13" t="s">
         <v>248</v>
       </c>
@@ -9158,7 +9164,7 @@
       <c r="G204" s="9">
         <v>0</v>
       </c>
-      <c r="H204" s="47"/>
+      <c r="H204" s="40"/>
       <c r="I204" s="13"/>
       <c r="J204" s="14"/>
     </row>
@@ -9184,7 +9190,7 @@
       <c r="G205" s="9">
         <v>0</v>
       </c>
-      <c r="H205" s="47"/>
+      <c r="H205" s="40"/>
       <c r="I205" s="13"/>
       <c r="J205" s="14" t="s">
         <v>817</v>
@@ -9212,7 +9218,7 @@
       <c r="G206" s="9">
         <v>0</v>
       </c>
-      <c r="H206" s="47"/>
+      <c r="H206" s="40"/>
       <c r="I206" s="13"/>
       <c r="J206" s="14"/>
     </row>
@@ -9238,7 +9244,7 @@
       <c r="G207" s="9">
         <v>0</v>
       </c>
-      <c r="H207" s="47"/>
+      <c r="H207" s="40"/>
       <c r="I207" s="13"/>
       <c r="J207" s="14"/>
     </row>
@@ -9264,7 +9270,7 @@
       <c r="G208" s="9">
         <v>0</v>
       </c>
-      <c r="H208" s="47"/>
+      <c r="H208" s="40"/>
       <c r="I208" s="13"/>
       <c r="J208" s="14" t="s">
         <v>818</v>
@@ -9292,7 +9298,7 @@
       <c r="G209" s="9">
         <v>0</v>
       </c>
-      <c r="H209" s="47"/>
+      <c r="H209" s="40"/>
       <c r="I209" s="13"/>
       <c r="J209" s="14"/>
     </row>
@@ -9318,7 +9324,7 @@
       <c r="G210" s="9">
         <v>0</v>
       </c>
-      <c r="H210" s="47"/>
+      <c r="H210" s="40"/>
       <c r="I210" s="13"/>
       <c r="J210" s="14"/>
     </row>
@@ -9344,7 +9350,7 @@
       <c r="G211" s="9">
         <v>0</v>
       </c>
-      <c r="H211" s="47"/>
+      <c r="H211" s="40"/>
       <c r="I211" s="13"/>
       <c r="J211" s="14"/>
     </row>
@@ -9370,7 +9376,7 @@
       <c r="G212" s="9">
         <v>0</v>
       </c>
-      <c r="H212" s="47"/>
+      <c r="H212" s="40"/>
       <c r="I212" s="13"/>
       <c r="J212" s="14"/>
     </row>
@@ -9396,7 +9402,7 @@
       <c r="G213" s="9">
         <v>0</v>
       </c>
-      <c r="H213" s="47"/>
+      <c r="H213" s="40"/>
       <c r="I213" s="13"/>
       <c r="J213" s="14"/>
     </row>
@@ -9422,7 +9428,7 @@
       <c r="G214" s="9">
         <v>0</v>
       </c>
-      <c r="H214" s="47"/>
+      <c r="H214" s="40"/>
       <c r="I214" s="13"/>
       <c r="J214" s="14"/>
     </row>
@@ -9448,7 +9454,7 @@
       <c r="G215" s="9">
         <v>0</v>
       </c>
-      <c r="H215" s="47"/>
+      <c r="H215" s="40"/>
       <c r="I215" s="13"/>
       <c r="J215" s="14"/>
     </row>
@@ -9474,7 +9480,7 @@
       <c r="G216" s="9">
         <v>0</v>
       </c>
-      <c r="H216" s="47"/>
+      <c r="H216" s="40"/>
       <c r="I216" s="13"/>
       <c r="J216" s="14"/>
     </row>
@@ -9500,7 +9506,7 @@
       <c r="G217" s="9">
         <v>0</v>
       </c>
-      <c r="H217" s="47"/>
+      <c r="H217" s="40"/>
       <c r="I217" s="13"/>
       <c r="J217" s="14" t="s">
         <v>819</v>
@@ -9528,7 +9534,7 @@
       <c r="G218" s="9">
         <v>0</v>
       </c>
-      <c r="H218" s="47"/>
+      <c r="H218" s="40"/>
       <c r="I218" s="13"/>
       <c r="J218" s="14" t="s">
         <v>820</v>
@@ -9556,7 +9562,7 @@
       <c r="G219" s="9">
         <v>0</v>
       </c>
-      <c r="H219" s="47"/>
+      <c r="H219" s="40"/>
       <c r="I219" s="13"/>
       <c r="J219" s="14"/>
     </row>
@@ -9582,7 +9588,7 @@
       <c r="G220" s="9">
         <v>0</v>
       </c>
-      <c r="H220" s="47"/>
+      <c r="H220" s="40"/>
       <c r="I220" s="13"/>
       <c r="J220" s="14" t="s">
         <v>821</v>
@@ -9610,7 +9616,7 @@
       <c r="G221" s="9">
         <v>0</v>
       </c>
-      <c r="H221" s="47"/>
+      <c r="H221" s="40"/>
       <c r="I221" s="13"/>
       <c r="J221" s="14"/>
     </row>
@@ -9636,7 +9642,7 @@
       <c r="G222" s="9">
         <v>0</v>
       </c>
-      <c r="H222" s="47"/>
+      <c r="H222" s="40"/>
       <c r="I222" s="13"/>
       <c r="J222" s="14"/>
     </row>
@@ -9662,7 +9668,7 @@
       <c r="G223" s="9">
         <v>0</v>
       </c>
-      <c r="H223" s="47"/>
+      <c r="H223" s="40"/>
       <c r="I223" s="13"/>
       <c r="J223" s="14"/>
     </row>
@@ -9688,7 +9694,7 @@
       <c r="G224" s="9">
         <v>0</v>
       </c>
-      <c r="H224" s="47"/>
+      <c r="H224" s="40"/>
       <c r="I224" s="13"/>
       <c r="J224" s="14"/>
     </row>
@@ -9714,7 +9720,7 @@
       <c r="G225" s="9">
         <v>0</v>
       </c>
-      <c r="H225" s="47"/>
+      <c r="H225" s="40"/>
       <c r="I225" s="13"/>
       <c r="J225" s="14"/>
     </row>
@@ -9740,7 +9746,7 @@
       <c r="G226" s="9">
         <v>0</v>
       </c>
-      <c r="H226" s="47"/>
+      <c r="H226" s="40"/>
       <c r="I226" s="13"/>
       <c r="J226" s="14"/>
     </row>
@@ -9766,7 +9772,7 @@
       <c r="G227" s="9">
         <v>0</v>
       </c>
-      <c r="H227" s="47"/>
+      <c r="H227" s="40"/>
       <c r="I227" s="13"/>
       <c r="J227" s="14"/>
     </row>
@@ -9792,7 +9798,7 @@
       <c r="G228" s="9">
         <v>0</v>
       </c>
-      <c r="H228" s="47"/>
+      <c r="H228" s="40"/>
       <c r="I228" s="13" t="s">
         <v>274</v>
       </c>
@@ -9820,7 +9826,7 @@
       <c r="G229" s="9">
         <v>0</v>
       </c>
-      <c r="H229" s="47"/>
+      <c r="H229" s="40"/>
       <c r="I229" s="13"/>
       <c r="J229" s="14"/>
     </row>
@@ -9846,7 +9852,7 @@
       <c r="G230" s="9">
         <v>0</v>
       </c>
-      <c r="H230" s="47"/>
+      <c r="H230" s="40"/>
       <c r="I230" s="13"/>
       <c r="J230" s="14"/>
     </row>
@@ -9872,7 +9878,7 @@
       <c r="G231" s="9">
         <v>0</v>
       </c>
-      <c r="H231" s="47"/>
+      <c r="H231" s="40"/>
       <c r="I231" s="13"/>
       <c r="J231" s="14"/>
     </row>
@@ -9898,7 +9904,7 @@
       <c r="G232" s="9">
         <v>0</v>
       </c>
-      <c r="H232" s="47"/>
+      <c r="H232" s="40"/>
       <c r="I232" s="13"/>
       <c r="J232" s="14"/>
     </row>
@@ -9924,7 +9930,7 @@
       <c r="G233" s="9">
         <v>0</v>
       </c>
-      <c r="H233" s="47"/>
+      <c r="H233" s="40"/>
       <c r="I233" s="13"/>
       <c r="J233" s="14"/>
     </row>
@@ -9950,7 +9956,7 @@
       <c r="G234" s="9">
         <v>0</v>
       </c>
-      <c r="H234" s="47"/>
+      <c r="H234" s="40"/>
       <c r="I234" s="13"/>
       <c r="J234" s="14"/>
     </row>
@@ -9976,7 +9982,7 @@
       <c r="G235" s="9">
         <v>0</v>
       </c>
-      <c r="H235" s="47"/>
+      <c r="H235" s="40"/>
       <c r="I235" s="13" t="s">
         <v>765</v>
       </c>
@@ -10006,7 +10012,7 @@
       <c r="G236" s="9">
         <v>0</v>
       </c>
-      <c r="H236" s="47"/>
+      <c r="H236" s="40"/>
       <c r="I236" s="13"/>
       <c r="J236" s="14"/>
     </row>
@@ -10032,7 +10038,7 @@
       <c r="G237" s="9">
         <v>0</v>
       </c>
-      <c r="H237" s="47"/>
+      <c r="H237" s="40"/>
       <c r="I237" s="13"/>
       <c r="J237" s="14"/>
     </row>
@@ -10058,7 +10064,7 @@
       <c r="G238" s="9">
         <v>0</v>
       </c>
-      <c r="H238" s="47"/>
+      <c r="H238" s="40"/>
       <c r="I238" s="13"/>
       <c r="J238" s="14"/>
     </row>
@@ -10084,7 +10090,7 @@
       <c r="G239" s="9">
         <v>0</v>
       </c>
-      <c r="H239" s="47"/>
+      <c r="H239" s="40"/>
       <c r="I239" s="13"/>
       <c r="J239" s="14" t="s">
         <v>822</v>
@@ -10112,7 +10118,7 @@
       <c r="G240" s="9">
         <v>0</v>
       </c>
-      <c r="H240" s="47"/>
+      <c r="H240" s="40"/>
       <c r="I240" s="13"/>
       <c r="J240" s="14"/>
     </row>
@@ -10138,7 +10144,7 @@
       <c r="G241" s="9">
         <v>0</v>
       </c>
-      <c r="H241" s="47"/>
+      <c r="H241" s="40"/>
       <c r="I241" s="13"/>
       <c r="J241" s="14"/>
     </row>
@@ -10164,7 +10170,7 @@
       <c r="G242" s="9">
         <v>0</v>
       </c>
-      <c r="H242" s="47"/>
+      <c r="H242" s="40"/>
       <c r="I242" s="13"/>
       <c r="J242" s="14"/>
     </row>
@@ -10190,7 +10196,7 @@
       <c r="G243" s="9">
         <v>0</v>
       </c>
-      <c r="H243" s="47"/>
+      <c r="H243" s="40"/>
       <c r="I243" s="13"/>
       <c r="J243" s="14"/>
     </row>
@@ -10216,7 +10222,7 @@
       <c r="G244" s="9">
         <v>0</v>
       </c>
-      <c r="H244" s="47"/>
+      <c r="H244" s="40"/>
       <c r="I244" s="13" t="s">
         <v>292</v>
       </c>
@@ -10246,7 +10252,7 @@
       <c r="G245" s="9">
         <v>0</v>
       </c>
-      <c r="H245" s="47"/>
+      <c r="H245" s="40"/>
       <c r="I245" s="13"/>
       <c r="J245" s="14"/>
     </row>
@@ -10272,7 +10278,7 @@
       <c r="G246" s="9">
         <v>0</v>
       </c>
-      <c r="H246" s="47"/>
+      <c r="H246" s="40"/>
       <c r="I246" s="13" t="s">
         <v>295</v>
       </c>
@@ -10302,7 +10308,7 @@
       <c r="G247" s="9">
         <v>0</v>
       </c>
-      <c r="H247" s="47"/>
+      <c r="H247" s="40"/>
       <c r="I247" s="13"/>
       <c r="J247" s="14"/>
     </row>
@@ -10328,7 +10334,7 @@
       <c r="G248" s="9">
         <v>0</v>
       </c>
-      <c r="H248" s="47"/>
+      <c r="H248" s="40"/>
       <c r="I248" s="13"/>
       <c r="J248" s="14"/>
     </row>
@@ -10354,7 +10360,7 @@
       <c r="G249" s="9">
         <v>0</v>
       </c>
-      <c r="H249" s="47"/>
+      <c r="H249" s="40"/>
       <c r="I249" s="13"/>
       <c r="J249" s="14"/>
     </row>
@@ -10380,7 +10386,7 @@
       <c r="G250" s="9">
         <v>0</v>
       </c>
-      <c r="H250" s="47"/>
+      <c r="H250" s="40"/>
       <c r="I250" s="13"/>
       <c r="J250" s="14"/>
     </row>
@@ -10406,7 +10412,7 @@
       <c r="G251" s="9">
         <v>0</v>
       </c>
-      <c r="H251" s="47"/>
+      <c r="H251" s="40"/>
       <c r="I251" s="13"/>
       <c r="J251" s="14"/>
     </row>
@@ -10432,7 +10438,7 @@
       <c r="G252" s="9">
         <v>0</v>
       </c>
-      <c r="H252" s="47"/>
+      <c r="H252" s="40"/>
       <c r="I252" s="13"/>
       <c r="J252" s="14"/>
     </row>
@@ -10458,7 +10464,7 @@
       <c r="G253" s="9">
         <v>0</v>
       </c>
-      <c r="H253" s="47"/>
+      <c r="H253" s="40"/>
       <c r="I253" s="13"/>
       <c r="J253" s="14"/>
     </row>
@@ -10484,7 +10490,7 @@
       <c r="G254" s="9">
         <v>0</v>
       </c>
-      <c r="H254" s="47"/>
+      <c r="H254" s="40"/>
       <c r="I254" s="13"/>
       <c r="J254" s="14"/>
     </row>
@@ -10510,7 +10516,7 @@
       <c r="G255" s="9">
         <v>0</v>
       </c>
-      <c r="H255" s="47"/>
+      <c r="H255" s="40"/>
       <c r="I255" s="13"/>
       <c r="J255" s="14"/>
     </row>
@@ -10536,7 +10542,7 @@
       <c r="G256" s="9">
         <v>0</v>
       </c>
-      <c r="H256" s="47"/>
+      <c r="H256" s="40"/>
       <c r="I256" s="13"/>
       <c r="J256" s="14"/>
     </row>
@@ -10562,7 +10568,7 @@
       <c r="G257" s="9">
         <v>0</v>
       </c>
-      <c r="H257" s="47"/>
+      <c r="H257" s="40"/>
       <c r="I257" s="13"/>
       <c r="J257" s="14"/>
     </row>
@@ -10588,7 +10594,7 @@
       <c r="G258" s="9">
         <v>0</v>
       </c>
-      <c r="H258" s="47"/>
+      <c r="H258" s="40"/>
       <c r="I258" s="13"/>
       <c r="J258" s="14"/>
     </row>
@@ -10614,7 +10620,7 @@
       <c r="G259" s="9">
         <v>0</v>
       </c>
-      <c r="H259" s="47"/>
+      <c r="H259" s="40"/>
       <c r="I259" s="13"/>
       <c r="J259" s="14"/>
     </row>
@@ -10640,7 +10646,7 @@
       <c r="G260" s="9">
         <v>0</v>
       </c>
-      <c r="H260" s="47"/>
+      <c r="H260" s="40"/>
       <c r="I260" s="13"/>
       <c r="J260" s="14"/>
     </row>
@@ -10666,7 +10672,7 @@
       <c r="G261" s="9">
         <v>0</v>
       </c>
-      <c r="H261" s="47"/>
+      <c r="H261" s="40"/>
       <c r="I261" s="13"/>
       <c r="J261" s="14"/>
     </row>
@@ -10692,7 +10698,7 @@
       <c r="G262" s="9">
         <v>0</v>
       </c>
-      <c r="H262" s="47"/>
+      <c r="H262" s="40"/>
       <c r="I262" s="13"/>
       <c r="J262" s="14"/>
     </row>
@@ -10718,7 +10724,7 @@
       <c r="G263" s="9">
         <v>0</v>
       </c>
-      <c r="H263" s="47"/>
+      <c r="H263" s="40"/>
       <c r="I263" s="13"/>
       <c r="J263" s="14"/>
     </row>
@@ -10744,7 +10750,7 @@
       <c r="G264" s="9">
         <v>0</v>
       </c>
-      <c r="H264" s="47"/>
+      <c r="H264" s="40"/>
       <c r="I264" s="13"/>
       <c r="J264" s="14"/>
     </row>
@@ -10770,7 +10776,7 @@
       <c r="G265" s="9">
         <v>0</v>
       </c>
-      <c r="H265" s="47"/>
+      <c r="H265" s="40"/>
       <c r="I265" s="13"/>
       <c r="J265" s="14"/>
     </row>
@@ -10796,7 +10802,7 @@
       <c r="G266" s="9">
         <v>0</v>
       </c>
-      <c r="H266" s="47"/>
+      <c r="H266" s="40"/>
       <c r="I266" s="13"/>
       <c r="J266" s="14"/>
     </row>
@@ -10822,7 +10828,7 @@
       <c r="G267" s="9">
         <v>0</v>
       </c>
-      <c r="H267" s="47"/>
+      <c r="H267" s="40"/>
       <c r="I267" s="13" t="s">
         <v>316</v>
       </c>
@@ -10852,7 +10858,7 @@
       <c r="G268" s="9">
         <v>0</v>
       </c>
-      <c r="H268" s="47"/>
+      <c r="H268" s="40"/>
       <c r="I268" s="13"/>
       <c r="J268" s="14"/>
     </row>
@@ -10878,7 +10884,7 @@
       <c r="G269" s="9">
         <v>0</v>
       </c>
-      <c r="H269" s="47"/>
+      <c r="H269" s="40"/>
       <c r="I269" s="13"/>
       <c r="J269" s="14"/>
     </row>
@@ -10904,7 +10910,7 @@
       <c r="G270" s="9">
         <v>0</v>
       </c>
-      <c r="H270" s="47"/>
+      <c r="H270" s="40"/>
       <c r="I270" s="13" t="s">
         <v>320</v>
       </c>
@@ -10934,7 +10940,7 @@
       <c r="G271" s="9">
         <v>0</v>
       </c>
-      <c r="H271" s="47"/>
+      <c r="H271" s="40"/>
       <c r="I271" s="13" t="s">
         <v>322</v>
       </c>
@@ -10964,7 +10970,7 @@
       <c r="G272" s="9">
         <v>0</v>
       </c>
-      <c r="H272" s="47"/>
+      <c r="H272" s="40"/>
       <c r="I272" s="13"/>
       <c r="J272" s="14"/>
     </row>
@@ -10990,7 +10996,7 @@
       <c r="G273" s="9">
         <v>0</v>
       </c>
-      <c r="H273" s="47"/>
+      <c r="H273" s="40"/>
       <c r="I273" s="13"/>
       <c r="J273" s="14"/>
     </row>
@@ -11016,7 +11022,7 @@
       <c r="G274" s="9">
         <v>0</v>
       </c>
-      <c r="H274" s="47"/>
+      <c r="H274" s="40"/>
       <c r="I274" s="13"/>
       <c r="J274" s="14"/>
     </row>
@@ -11042,7 +11048,7 @@
       <c r="G275" s="9">
         <v>0</v>
       </c>
-      <c r="H275" s="47"/>
+      <c r="H275" s="40"/>
       <c r="I275" s="13"/>
       <c r="J275" s="14"/>
     </row>
@@ -11068,7 +11074,7 @@
       <c r="G276" s="9">
         <v>0</v>
       </c>
-      <c r="H276" s="47"/>
+      <c r="H276" s="40"/>
       <c r="I276" s="13"/>
       <c r="J276" s="14"/>
     </row>
@@ -11094,7 +11100,7 @@
       <c r="G277" s="9">
         <v>0</v>
       </c>
-      <c r="H277" s="47"/>
+      <c r="H277" s="40"/>
       <c r="I277" s="13"/>
       <c r="J277" s="14"/>
     </row>
@@ -11120,7 +11126,7 @@
       <c r="G278" s="9">
         <v>0</v>
       </c>
-      <c r="H278" s="47"/>
+      <c r="H278" s="40"/>
       <c r="I278" s="13"/>
       <c r="J278" s="14" t="s">
         <v>828</v>
@@ -11148,7 +11154,7 @@
       <c r="G279" s="9">
         <v>0</v>
       </c>
-      <c r="H279" s="47"/>
+      <c r="H279" s="40"/>
       <c r="I279" s="13"/>
       <c r="J279" s="14"/>
     </row>
@@ -11174,7 +11180,7 @@
       <c r="G280" s="9">
         <v>0</v>
       </c>
-      <c r="H280" s="47"/>
+      <c r="H280" s="40"/>
       <c r="I280" s="13"/>
       <c r="J280" s="14"/>
     </row>
@@ -11200,7 +11206,7 @@
       <c r="G281" s="9">
         <v>0</v>
       </c>
-      <c r="H281" s="47"/>
+      <c r="H281" s="40"/>
       <c r="I281" s="13"/>
       <c r="J281" s="14"/>
     </row>
@@ -11226,7 +11232,7 @@
       <c r="G282" s="9">
         <v>0</v>
       </c>
-      <c r="H282" s="47"/>
+      <c r="H282" s="40"/>
       <c r="I282" s="13" t="s">
         <v>334</v>
       </c>
@@ -11254,7 +11260,7 @@
       <c r="G283" s="9">
         <v>0</v>
       </c>
-      <c r="H283" s="47"/>
+      <c r="H283" s="40"/>
       <c r="I283" s="13" t="s">
         <v>336</v>
       </c>
@@ -11284,7 +11290,7 @@
       <c r="G284" s="9">
         <v>0</v>
       </c>
-      <c r="H284" s="47"/>
+      <c r="H284" s="40"/>
       <c r="I284" s="13" t="s">
         <v>338</v>
       </c>
@@ -11314,7 +11320,7 @@
       <c r="G285" s="9">
         <v>0</v>
       </c>
-      <c r="H285" s="47"/>
+      <c r="H285" s="40"/>
       <c r="I285" s="13"/>
       <c r="J285" s="14"/>
     </row>
@@ -11340,7 +11346,7 @@
       <c r="G286" s="9">
         <v>0</v>
       </c>
-      <c r="H286" s="47"/>
+      <c r="H286" s="40"/>
       <c r="I286" s="13"/>
       <c r="J286" s="14" t="s">
         <v>831</v>
@@ -11368,7 +11374,7 @@
       <c r="G287" s="9">
         <v>0</v>
       </c>
-      <c r="H287" s="47"/>
+      <c r="H287" s="40"/>
       <c r="I287" s="13"/>
       <c r="J287" s="14"/>
     </row>
@@ -11394,7 +11400,7 @@
       <c r="G288" s="9">
         <v>0</v>
       </c>
-      <c r="H288" s="47"/>
+      <c r="H288" s="40"/>
       <c r="I288" s="13"/>
       <c r="J288" s="14"/>
     </row>
@@ -11420,7 +11426,7 @@
       <c r="G289" s="9">
         <v>0</v>
       </c>
-      <c r="H289" s="47"/>
+      <c r="H289" s="40"/>
       <c r="I289" s="13"/>
       <c r="J289" s="14"/>
     </row>
@@ -11446,7 +11452,7 @@
       <c r="G290" s="9">
         <v>0</v>
       </c>
-      <c r="H290" s="47"/>
+      <c r="H290" s="40"/>
       <c r="I290" s="13"/>
       <c r="J290" s="14"/>
     </row>
@@ -11472,7 +11478,7 @@
       <c r="G291" s="9">
         <v>0</v>
       </c>
-      <c r="H291" s="47"/>
+      <c r="H291" s="40"/>
       <c r="I291" s="13"/>
       <c r="J291" s="14"/>
     </row>
@@ -11498,7 +11504,7 @@
       <c r="G292" s="9">
         <v>0</v>
       </c>
-      <c r="H292" s="47"/>
+      <c r="H292" s="40"/>
       <c r="I292" s="13" t="s">
         <v>347</v>
       </c>
@@ -11526,7 +11532,7 @@
       <c r="G293" s="9">
         <v>0</v>
       </c>
-      <c r="H293" s="47"/>
+      <c r="H293" s="40"/>
       <c r="I293" s="13" t="s">
         <v>349</v>
       </c>
@@ -11554,7 +11560,7 @@
       <c r="G294" s="9">
         <v>0</v>
       </c>
-      <c r="H294" s="47"/>
+      <c r="H294" s="40"/>
       <c r="I294" s="13" t="s">
         <v>351</v>
       </c>
@@ -11584,7 +11590,7 @@
       <c r="G295" s="9">
         <v>0</v>
       </c>
-      <c r="H295" s="47"/>
+      <c r="H295" s="40"/>
       <c r="I295" s="13"/>
       <c r="J295" s="14"/>
     </row>
@@ -11610,7 +11616,7 @@
       <c r="G296" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H296" s="47"/>
+      <c r="H296" s="40"/>
       <c r="I296" s="13"/>
       <c r="J296" s="14"/>
     </row>
@@ -11636,7 +11642,7 @@
       <c r="G297" s="9">
         <v>0</v>
       </c>
-      <c r="H297" s="47"/>
+      <c r="H297" s="40"/>
       <c r="I297" s="13"/>
       <c r="J297" s="14"/>
     </row>
@@ -11662,7 +11668,7 @@
       <c r="G298" s="9">
         <v>0</v>
       </c>
-      <c r="H298" s="47"/>
+      <c r="H298" s="40"/>
       <c r="I298" s="13"/>
       <c r="J298" s="14"/>
     </row>
@@ -11688,7 +11694,7 @@
       <c r="G299" s="9">
         <v>0</v>
       </c>
-      <c r="H299" s="47"/>
+      <c r="H299" s="40"/>
       <c r="I299" s="13"/>
       <c r="J299" s="14"/>
     </row>
@@ -11714,7 +11720,7 @@
       <c r="G300" s="9">
         <v>0</v>
       </c>
-      <c r="H300" s="47"/>
+      <c r="H300" s="40"/>
       <c r="I300" s="13"/>
       <c r="J300" s="14"/>
     </row>
@@ -11740,7 +11746,7 @@
       <c r="G301" s="9">
         <v>0</v>
       </c>
-      <c r="H301" s="47"/>
+      <c r="H301" s="40"/>
       <c r="I301" s="13"/>
       <c r="J301" s="14"/>
     </row>
@@ -11766,7 +11772,7 @@
       <c r="G302" s="9">
         <v>0</v>
       </c>
-      <c r="H302" s="47"/>
+      <c r="H302" s="40"/>
       <c r="I302" s="13" t="s">
         <v>360</v>
       </c>
@@ -11794,7 +11800,7 @@
       <c r="G303" s="9">
         <v>0</v>
       </c>
-      <c r="H303" s="47"/>
+      <c r="H303" s="40"/>
       <c r="I303" s="13"/>
       <c r="J303" s="14"/>
     </row>
@@ -11820,7 +11826,7 @@
       <c r="G304" s="9">
         <v>0</v>
       </c>
-      <c r="H304" s="47"/>
+      <c r="H304" s="40"/>
       <c r="I304" s="13"/>
       <c r="J304" s="14"/>
     </row>
@@ -11846,7 +11852,7 @@
       <c r="G305" s="9">
         <v>0</v>
       </c>
-      <c r="H305" s="47"/>
+      <c r="H305" s="40"/>
       <c r="I305" s="13"/>
       <c r="J305" s="14"/>
     </row>
@@ -11872,7 +11878,7 @@
       <c r="G306" s="9">
         <v>0</v>
       </c>
-      <c r="H306" s="47"/>
+      <c r="H306" s="40"/>
       <c r="I306" s="13"/>
       <c r="J306" s="14"/>
     </row>
@@ -11898,7 +11904,7 @@
       <c r="G307" s="9">
         <v>0</v>
       </c>
-      <c r="H307" s="47"/>
+      <c r="H307" s="40"/>
       <c r="I307" s="13"/>
       <c r="J307" s="14"/>
     </row>
@@ -11924,7 +11930,7 @@
       <c r="G308" s="9">
         <v>0</v>
       </c>
-      <c r="H308" s="47"/>
+      <c r="H308" s="40"/>
       <c r="I308" s="13"/>
       <c r="J308" s="14"/>
     </row>
@@ -11950,7 +11956,7 @@
       <c r="G309" s="9">
         <v>0</v>
       </c>
-      <c r="H309" s="47"/>
+      <c r="H309" s="40"/>
       <c r="I309" s="13"/>
       <c r="J309" s="14"/>
     </row>
@@ -11976,7 +11982,7 @@
       <c r="G310" s="9">
         <v>0</v>
       </c>
-      <c r="H310" s="47"/>
+      <c r="H310" s="40"/>
       <c r="I310" s="13"/>
       <c r="J310" s="14"/>
     </row>
@@ -12002,7 +12008,7 @@
       <c r="G311" s="9">
         <v>0</v>
       </c>
-      <c r="H311" s="47"/>
+      <c r="H311" s="40"/>
       <c r="I311" s="13"/>
       <c r="J311" s="14"/>
     </row>
@@ -12028,7 +12034,7 @@
       <c r="G312" s="9">
         <v>0</v>
       </c>
-      <c r="H312" s="47"/>
+      <c r="H312" s="40"/>
       <c r="I312" s="13"/>
       <c r="J312" s="14"/>
     </row>
@@ -12054,7 +12060,7 @@
       <c r="G313" s="9">
         <v>0</v>
       </c>
-      <c r="H313" s="47"/>
+      <c r="H313" s="40"/>
       <c r="I313" s="13"/>
       <c r="J313" s="14"/>
     </row>
@@ -12080,7 +12086,7 @@
       <c r="G314" s="9">
         <v>0</v>
       </c>
-      <c r="H314" s="47"/>
+      <c r="H314" s="40"/>
       <c r="I314" s="13"/>
       <c r="J314" s="14"/>
     </row>
@@ -12106,7 +12112,7 @@
       <c r="G315" s="9">
         <v>0</v>
       </c>
-      <c r="H315" s="47"/>
+      <c r="H315" s="40"/>
       <c r="I315" s="13"/>
       <c r="J315" s="14"/>
     </row>
@@ -12132,7 +12138,7 @@
       <c r="G316" s="9">
         <v>0</v>
       </c>
-      <c r="H316" s="47"/>
+      <c r="H316" s="40"/>
       <c r="I316" s="13"/>
       <c r="J316" s="14"/>
     </row>
@@ -12158,7 +12164,7 @@
       <c r="G317" s="9">
         <v>0</v>
       </c>
-      <c r="H317" s="47"/>
+      <c r="H317" s="40"/>
       <c r="I317" s="13"/>
       <c r="J317" s="14"/>
     </row>
@@ -12184,7 +12190,7 @@
       <c r="G318" s="9">
         <v>0</v>
       </c>
-      <c r="H318" s="47"/>
+      <c r="H318" s="40"/>
       <c r="I318" s="13"/>
       <c r="J318" s="14"/>
     </row>
@@ -12210,7 +12216,7 @@
       <c r="G319" s="9">
         <v>0</v>
       </c>
-      <c r="H319" s="47"/>
+      <c r="H319" s="40"/>
       <c r="I319" s="13"/>
       <c r="J319" s="14" t="s">
         <v>833</v>
@@ -12238,7 +12244,7 @@
       <c r="G320" s="9">
         <v>0</v>
       </c>
-      <c r="H320" s="47"/>
+      <c r="H320" s="40"/>
       <c r="I320" s="13"/>
       <c r="J320" s="14"/>
     </row>
@@ -12264,7 +12270,7 @@
       <c r="G321" s="9">
         <v>0</v>
       </c>
-      <c r="H321" s="47"/>
+      <c r="H321" s="40"/>
       <c r="I321" s="13"/>
       <c r="J321" s="14"/>
     </row>
@@ -12290,7 +12296,7 @@
       <c r="G322" s="9">
         <v>0</v>
       </c>
-      <c r="H322" s="47"/>
+      <c r="H322" s="40"/>
       <c r="I322" s="13"/>
       <c r="J322" s="14"/>
     </row>
@@ -12316,7 +12322,7 @@
       <c r="G323" s="9">
         <v>0</v>
       </c>
-      <c r="H323" s="47"/>
+      <c r="H323" s="40"/>
       <c r="I323" s="13"/>
       <c r="J323" s="14"/>
     </row>
@@ -12342,7 +12348,7 @@
       <c r="G324" s="9">
         <v>0</v>
       </c>
-      <c r="H324" s="47"/>
+      <c r="H324" s="40"/>
       <c r="I324" s="13"/>
       <c r="J324" s="14"/>
     </row>
@@ -12368,7 +12374,7 @@
       <c r="G325" s="9">
         <v>0</v>
       </c>
-      <c r="H325" s="47"/>
+      <c r="H325" s="40"/>
       <c r="I325" s="13" t="s">
         <v>384</v>
       </c>
@@ -12398,7 +12404,7 @@
       <c r="G326" s="9">
         <v>0</v>
       </c>
-      <c r="H326" s="47"/>
+      <c r="H326" s="40"/>
       <c r="I326" s="13" t="s">
         <v>386</v>
       </c>
@@ -12428,7 +12434,7 @@
       <c r="G327" s="9">
         <v>0</v>
       </c>
-      <c r="H327" s="47"/>
+      <c r="H327" s="40"/>
       <c r="I327" s="13"/>
       <c r="J327" s="14"/>
     </row>
@@ -12454,7 +12460,7 @@
       <c r="G328" s="9">
         <v>0</v>
       </c>
-      <c r="H328" s="47"/>
+      <c r="H328" s="40"/>
       <c r="I328" s="13"/>
       <c r="J328" s="14"/>
     </row>
@@ -12480,7 +12486,7 @@
       <c r="G329" s="9">
         <v>0</v>
       </c>
-      <c r="H329" s="47"/>
+      <c r="H329" s="40"/>
       <c r="I329" s="13"/>
       <c r="J329" s="14"/>
     </row>
@@ -12506,7 +12512,7 @@
       <c r="G330" s="9">
         <v>0</v>
       </c>
-      <c r="H330" s="47"/>
+      <c r="H330" s="40"/>
       <c r="I330" s="13"/>
       <c r="J330" s="14"/>
     </row>
@@ -12532,7 +12538,7 @@
       <c r="G331" s="9">
         <v>0</v>
       </c>
-      <c r="H331" s="47"/>
+      <c r="H331" s="40"/>
       <c r="I331" s="13"/>
       <c r="J331" s="14" t="s">
         <v>836</v>
@@ -12560,7 +12566,7 @@
       <c r="G332" s="9">
         <v>0</v>
       </c>
-      <c r="H332" s="47"/>
+      <c r="H332" s="40"/>
       <c r="I332" s="13"/>
       <c r="J332" s="14" t="s">
         <v>837</v>
@@ -12588,7 +12594,7 @@
       <c r="G333" s="9">
         <v>0</v>
       </c>
-      <c r="H333" s="47"/>
+      <c r="H333" s="40"/>
       <c r="I333" s="13"/>
       <c r="J333" s="14"/>
     </row>
@@ -12614,7 +12620,7 @@
       <c r="G334" s="9">
         <v>0</v>
       </c>
-      <c r="H334" s="47"/>
+      <c r="H334" s="40"/>
       <c r="I334" s="13"/>
       <c r="J334" s="14"/>
     </row>
@@ -12640,7 +12646,7 @@
       <c r="G335" s="9">
         <v>0</v>
       </c>
-      <c r="H335" s="47"/>
+      <c r="H335" s="40"/>
       <c r="I335" s="13"/>
       <c r="J335" s="14" t="s">
         <v>838</v>
@@ -12668,7 +12674,7 @@
       <c r="G336" s="9">
         <v>0</v>
       </c>
-      <c r="H336" s="47"/>
+      <c r="H336" s="40"/>
       <c r="I336" s="13" t="s">
         <v>397</v>
       </c>
@@ -12696,7 +12702,7 @@
       <c r="G337" s="9">
         <v>0</v>
       </c>
-      <c r="H337" s="47"/>
+      <c r="H337" s="40"/>
       <c r="I337" s="13"/>
       <c r="J337" s="14" t="s">
         <v>839</v>
@@ -12724,7 +12730,7 @@
       <c r="G338" s="9">
         <v>0</v>
       </c>
-      <c r="H338" s="47"/>
+      <c r="H338" s="40"/>
       <c r="I338" s="13"/>
       <c r="J338" s="14"/>
     </row>
@@ -12750,7 +12756,7 @@
       <c r="G339" s="9">
         <v>0</v>
       </c>
-      <c r="H339" s="47"/>
+      <c r="H339" s="40"/>
       <c r="I339" s="13"/>
       <c r="J339" s="14"/>
     </row>
@@ -12776,7 +12782,7 @@
       <c r="G340" s="9">
         <v>0</v>
       </c>
-      <c r="H340" s="47"/>
+      <c r="H340" s="40"/>
       <c r="I340" s="13"/>
       <c r="J340" s="14"/>
     </row>
@@ -12802,7 +12808,7 @@
       <c r="G341" s="9">
         <v>0</v>
       </c>
-      <c r="H341" s="47"/>
+      <c r="H341" s="40"/>
       <c r="I341" s="13" t="s">
         <v>403</v>
       </c>
@@ -12830,7 +12836,7 @@
       <c r="G342" s="9">
         <v>0</v>
       </c>
-      <c r="H342" s="47"/>
+      <c r="H342" s="40"/>
       <c r="I342" s="13"/>
       <c r="J342" s="14"/>
     </row>
@@ -12856,7 +12862,7 @@
       <c r="G343" s="9">
         <v>0</v>
       </c>
-      <c r="H343" s="47"/>
+      <c r="H343" s="40"/>
       <c r="I343" s="13"/>
       <c r="J343" s="14"/>
     </row>
@@ -12882,7 +12888,7 @@
       <c r="G344" s="9">
         <v>0</v>
       </c>
-      <c r="H344" s="47"/>
+      <c r="H344" s="40"/>
       <c r="I344" s="13"/>
       <c r="J344" s="14"/>
     </row>
@@ -12908,7 +12914,7 @@
       <c r="G345" s="9">
         <v>0</v>
       </c>
-      <c r="H345" s="47"/>
+      <c r="H345" s="40"/>
       <c r="I345" s="13"/>
       <c r="J345" s="14"/>
     </row>
@@ -12934,7 +12940,7 @@
       <c r="G346" s="9">
         <v>0</v>
       </c>
-      <c r="H346" s="47"/>
+      <c r="H346" s="40"/>
       <c r="I346" s="13"/>
       <c r="J346" s="14"/>
     </row>
@@ -12960,7 +12966,7 @@
       <c r="G347" s="9">
         <v>0</v>
       </c>
-      <c r="H347" s="47"/>
+      <c r="H347" s="40"/>
       <c r="I347" s="13"/>
       <c r="J347" s="14"/>
     </row>
@@ -12986,7 +12992,7 @@
       <c r="G348" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="H348" s="47"/>
+      <c r="H348" s="40"/>
       <c r="I348" s="13"/>
       <c r="J348" s="14"/>
     </row>
@@ -13012,7 +13018,7 @@
       <c r="G349" s="9">
         <v>0</v>
       </c>
-      <c r="H349" s="47"/>
+      <c r="H349" s="40"/>
       <c r="I349" s="13"/>
       <c r="J349" s="14"/>
     </row>
@@ -13038,7 +13044,7 @@
       <c r="G350" s="9">
         <v>0</v>
       </c>
-      <c r="H350" s="47"/>
+      <c r="H350" s="40"/>
       <c r="I350" s="13" t="s">
         <v>413</v>
       </c>
@@ -13066,7 +13072,7 @@
       <c r="G351" s="9">
         <v>0</v>
       </c>
-      <c r="H351" s="47"/>
+      <c r="H351" s="40"/>
       <c r="I351" s="13"/>
       <c r="J351" s="14"/>
     </row>
@@ -13092,7 +13098,7 @@
       <c r="G352" s="9">
         <v>0</v>
       </c>
-      <c r="H352" s="47"/>
+      <c r="H352" s="40"/>
       <c r="I352" s="13"/>
       <c r="J352" s="14" t="s">
         <v>840</v>
@@ -13120,7 +13126,7 @@
       <c r="G353" s="9">
         <v>0</v>
       </c>
-      <c r="H353" s="47"/>
+      <c r="H353" s="40"/>
       <c r="I353" s="13"/>
       <c r="J353" s="14"/>
     </row>
@@ -13146,7 +13152,7 @@
       <c r="G354" s="9">
         <v>0</v>
       </c>
-      <c r="H354" s="47"/>
+      <c r="H354" s="40"/>
       <c r="I354" s="13"/>
       <c r="J354" s="14"/>
     </row>
@@ -13172,7 +13178,7 @@
       <c r="G355" s="9">
         <v>0</v>
       </c>
-      <c r="H355" s="47"/>
+      <c r="H355" s="40"/>
       <c r="I355" s="13" t="s">
         <v>419</v>
       </c>
@@ -13202,7 +13208,7 @@
       <c r="G356" s="9">
         <v>0</v>
       </c>
-      <c r="H356" s="47"/>
+      <c r="H356" s="40"/>
       <c r="I356" s="13"/>
       <c r="J356" s="14"/>
     </row>
@@ -13228,7 +13234,7 @@
       <c r="G357" s="9">
         <v>0</v>
       </c>
-      <c r="H357" s="47"/>
+      <c r="H357" s="40"/>
       <c r="I357" s="13"/>
       <c r="J357" s="14"/>
     </row>
@@ -13254,7 +13260,7 @@
       <c r="G358" s="9">
         <v>0</v>
       </c>
-      <c r="H358" s="47"/>
+      <c r="H358" s="40"/>
       <c r="I358" s="13"/>
       <c r="J358" s="14"/>
     </row>
@@ -13280,7 +13286,7 @@
       <c r="G359" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H359" s="47"/>
+      <c r="H359" s="40"/>
       <c r="I359" s="13"/>
       <c r="J359" s="14"/>
     </row>
@@ -13306,7 +13312,7 @@
       <c r="G360" s="9">
         <v>0</v>
       </c>
-      <c r="H360" s="47"/>
+      <c r="H360" s="40"/>
       <c r="I360" s="13"/>
       <c r="J360" s="14" t="s">
         <v>842</v>
@@ -13334,7 +13340,7 @@
       <c r="G361" s="9">
         <v>0</v>
       </c>
-      <c r="H361" s="47"/>
+      <c r="H361" s="40"/>
       <c r="I361" s="13"/>
       <c r="J361" s="14" t="s">
         <v>843</v>
@@ -13362,7 +13368,7 @@
       <c r="G362" s="9">
         <v>0</v>
       </c>
-      <c r="H362" s="47"/>
+      <c r="H362" s="40"/>
       <c r="I362" s="13"/>
       <c r="J362" s="14"/>
     </row>
@@ -13388,7 +13394,7 @@
       <c r="G363" s="9">
         <v>0</v>
       </c>
-      <c r="H363" s="47"/>
+      <c r="H363" s="40"/>
       <c r="I363" s="13"/>
       <c r="J363" s="14"/>
     </row>
@@ -13414,7 +13420,7 @@
       <c r="G364" s="9">
         <v>0</v>
       </c>
-      <c r="H364" s="47"/>
+      <c r="H364" s="40"/>
       <c r="I364" s="13"/>
       <c r="J364" s="14"/>
     </row>
@@ -13440,7 +13446,7 @@
       <c r="G365" s="9">
         <v>0</v>
       </c>
-      <c r="H365" s="47"/>
+      <c r="H365" s="40"/>
       <c r="I365" s="13"/>
       <c r="J365" s="14"/>
     </row>
@@ -13466,7 +13472,7 @@
       <c r="G366" s="9">
         <v>0</v>
       </c>
-      <c r="H366" s="47"/>
+      <c r="H366" s="40"/>
       <c r="I366" s="13"/>
       <c r="J366" s="14"/>
     </row>
@@ -13492,7 +13498,7 @@
       <c r="G367" s="9">
         <v>0</v>
       </c>
-      <c r="H367" s="47"/>
+      <c r="H367" s="40"/>
       <c r="I367" s="13"/>
       <c r="J367" s="14"/>
     </row>
@@ -13518,7 +13524,7 @@
       <c r="G368" s="9">
         <v>0</v>
       </c>
-      <c r="H368" s="47"/>
+      <c r="H368" s="40"/>
       <c r="I368" s="13"/>
       <c r="J368" s="14"/>
     </row>
@@ -13544,7 +13550,7 @@
       <c r="G369" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H369" s="47"/>
+      <c r="H369" s="40"/>
       <c r="I369" s="15"/>
       <c r="J369" s="16"/>
     </row>
@@ -13570,7 +13576,7 @@
       <c r="G370" s="9">
         <v>0</v>
       </c>
-      <c r="H370" s="47"/>
+      <c r="H370" s="40"/>
       <c r="I370" s="13"/>
       <c r="J370" s="14"/>
     </row>
@@ -13596,7 +13602,7 @@
       <c r="G371" s="9">
         <v>0</v>
       </c>
-      <c r="H371" s="47"/>
+      <c r="H371" s="40"/>
       <c r="I371" s="13"/>
       <c r="J371" s="14"/>
     </row>
@@ -13622,7 +13628,7 @@
       <c r="G372" s="9">
         <v>0</v>
       </c>
-      <c r="H372" s="47"/>
+      <c r="H372" s="40"/>
       <c r="I372" s="13"/>
       <c r="J372" s="14"/>
     </row>
@@ -13648,7 +13654,7 @@
       <c r="G373" s="9">
         <v>0</v>
       </c>
-      <c r="H373" s="47"/>
+      <c r="H373" s="40"/>
       <c r="I373" s="13"/>
       <c r="J373" s="14"/>
     </row>
@@ -13674,7 +13680,7 @@
       <c r="G374" s="9">
         <v>0</v>
       </c>
-      <c r="H374" s="47"/>
+      <c r="H374" s="40"/>
       <c r="I374" s="13"/>
       <c r="J374" s="14"/>
     </row>
@@ -13700,7 +13706,7 @@
       <c r="G375" s="9">
         <v>0</v>
       </c>
-      <c r="H375" s="47"/>
+      <c r="H375" s="40"/>
       <c r="I375" s="13"/>
       <c r="J375" s="14" t="s">
         <v>844</v>
@@ -13728,7 +13734,7 @@
       <c r="G376" s="9">
         <v>0</v>
       </c>
-      <c r="H376" s="47"/>
+      <c r="H376" s="40"/>
       <c r="I376" s="13"/>
       <c r="J376" s="14"/>
     </row>
@@ -13754,7 +13760,7 @@
       <c r="G377" s="9">
         <v>0</v>
       </c>
-      <c r="H377" s="47"/>
+      <c r="H377" s="40"/>
       <c r="I377" s="13"/>
       <c r="J377" s="14"/>
     </row>
@@ -13780,7 +13786,7 @@
       <c r="G378" s="9">
         <v>0</v>
       </c>
-      <c r="H378" s="47"/>
+      <c r="H378" s="40"/>
       <c r="I378" s="13"/>
       <c r="J378" s="14"/>
     </row>
@@ -13806,7 +13812,7 @@
       <c r="G379" s="9">
         <v>0</v>
       </c>
-      <c r="H379" s="47"/>
+      <c r="H379" s="40"/>
       <c r="I379" s="13" t="s">
         <v>443</v>
       </c>
@@ -13836,7 +13842,7 @@
       <c r="G380" s="9">
         <v>0</v>
       </c>
-      <c r="H380" s="47"/>
+      <c r="H380" s="40"/>
       <c r="I380" s="13" t="s">
         <v>441</v>
       </c>
@@ -13866,7 +13872,7 @@
       <c r="G381" s="9">
         <v>0</v>
       </c>
-      <c r="H381" s="47"/>
+      <c r="H381" s="40"/>
       <c r="I381" s="13"/>
       <c r="J381" s="14"/>
     </row>
@@ -13892,7 +13898,7 @@
       <c r="G382" s="9">
         <v>0</v>
       </c>
-      <c r="H382" s="47"/>
+      <c r="H382" s="40"/>
       <c r="I382" s="13"/>
       <c r="J382" s="14"/>
     </row>
@@ -13918,7 +13924,7 @@
       <c r="G383" s="9">
         <v>0</v>
       </c>
-      <c r="H383" s="47"/>
+      <c r="H383" s="40"/>
       <c r="I383" s="13"/>
       <c r="J383" s="14"/>
     </row>
@@ -13944,7 +13950,7 @@
       <c r="G384" s="9">
         <v>0</v>
       </c>
-      <c r="H384" s="47"/>
+      <c r="H384" s="40"/>
       <c r="I384" s="13"/>
       <c r="J384" s="14"/>
     </row>
@@ -13970,7 +13976,7 @@
       <c r="G385" s="9">
         <v>0</v>
       </c>
-      <c r="H385" s="47"/>
+      <c r="H385" s="40"/>
       <c r="I385" s="13"/>
       <c r="J385" s="14"/>
     </row>
@@ -13996,7 +14002,7 @@
       <c r="G386" s="9">
         <v>0</v>
       </c>
-      <c r="H386" s="47"/>
+      <c r="H386" s="40"/>
       <c r="I386" s="13" t="s">
         <v>449</v>
       </c>
@@ -14024,7 +14030,7 @@
       <c r="G387" s="9">
         <v>0</v>
       </c>
-      <c r="H387" s="47"/>
+      <c r="H387" s="40"/>
       <c r="I387" s="13"/>
       <c r="J387" s="14"/>
     </row>
@@ -14050,7 +14056,7 @@
       <c r="G388" s="9">
         <v>0</v>
       </c>
-      <c r="H388" s="47"/>
+      <c r="H388" s="40"/>
       <c r="I388" s="13"/>
       <c r="J388" s="14"/>
     </row>
@@ -14076,7 +14082,7 @@
       <c r="G389" s="9">
         <v>0</v>
       </c>
-      <c r="H389" s="47"/>
+      <c r="H389" s="40"/>
       <c r="I389" s="13" t="s">
         <v>453</v>
       </c>
@@ -14104,7 +14110,7 @@
       <c r="G390" s="9">
         <v>0</v>
       </c>
-      <c r="H390" s="47"/>
+      <c r="H390" s="40"/>
       <c r="I390" s="13"/>
       <c r="J390" s="14"/>
     </row>
@@ -14130,7 +14136,7 @@
       <c r="G391" s="9">
         <v>0</v>
       </c>
-      <c r="H391" s="47"/>
+      <c r="H391" s="40"/>
       <c r="I391" s="13"/>
       <c r="J391" s="14"/>
     </row>
@@ -14156,7 +14162,7 @@
       <c r="G392" s="9">
         <v>0</v>
       </c>
-      <c r="H392" s="47"/>
+      <c r="H392" s="40"/>
       <c r="I392" s="13"/>
       <c r="J392" s="14"/>
     </row>
@@ -14182,7 +14188,7 @@
       <c r="G393" s="9">
         <v>0</v>
       </c>
-      <c r="H393" s="47"/>
+      <c r="H393" s="40"/>
       <c r="I393" s="13"/>
       <c r="J393" s="14"/>
     </row>
@@ -14208,7 +14214,7 @@
       <c r="G394" s="9">
         <v>0</v>
       </c>
-      <c r="H394" s="47"/>
+      <c r="H394" s="40"/>
       <c r="I394" s="13"/>
       <c r="J394" s="14" t="s">
         <v>845</v>
@@ -14236,7 +14242,7 @@
       <c r="G395" s="9">
         <v>0</v>
       </c>
-      <c r="H395" s="47"/>
+      <c r="H395" s="40"/>
       <c r="I395" s="13"/>
       <c r="J395" s="14" t="s">
         <v>846</v>
@@ -14264,7 +14270,7 @@
       <c r="G396" s="9">
         <v>0</v>
       </c>
-      <c r="H396" s="47"/>
+      <c r="H396" s="40"/>
       <c r="I396" s="13"/>
       <c r="J396" s="14"/>
     </row>
@@ -14290,7 +14296,7 @@
       <c r="G397" s="9">
         <v>0</v>
       </c>
-      <c r="H397" s="47"/>
+      <c r="H397" s="40"/>
       <c r="I397" s="13"/>
       <c r="J397" s="14"/>
     </row>
@@ -14316,7 +14322,7 @@
       <c r="G398" s="9">
         <v>0</v>
       </c>
-      <c r="H398" s="47"/>
+      <c r="H398" s="40"/>
       <c r="I398" s="13"/>
       <c r="J398" s="14"/>
     </row>
@@ -14342,7 +14348,7 @@
       <c r="G399" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H399" s="47"/>
+      <c r="H399" s="40"/>
       <c r="I399" s="13"/>
       <c r="J399" s="14"/>
     </row>
@@ -14368,7 +14374,7 @@
       <c r="G400" s="9">
         <v>0</v>
       </c>
-      <c r="H400" s="47"/>
+      <c r="H400" s="40"/>
       <c r="I400" s="13"/>
       <c r="J400" s="14"/>
     </row>
@@ -14394,7 +14400,7 @@
       <c r="G401" s="9">
         <v>0</v>
       </c>
-      <c r="H401" s="47"/>
+      <c r="H401" s="40"/>
       <c r="I401" s="13"/>
       <c r="J401" s="14"/>
     </row>
@@ -14420,7 +14426,7 @@
       <c r="G402" s="9">
         <v>0</v>
       </c>
-      <c r="H402" s="47"/>
+      <c r="H402" s="40"/>
       <c r="I402" s="13"/>
       <c r="J402" s="14"/>
     </row>
@@ -14446,7 +14452,7 @@
       <c r="G403" s="9">
         <v>0</v>
       </c>
-      <c r="H403" s="47"/>
+      <c r="H403" s="40"/>
       <c r="I403" s="13"/>
       <c r="J403" s="14"/>
     </row>
@@ -14472,7 +14478,7 @@
       <c r="G404" s="9">
         <v>0</v>
       </c>
-      <c r="H404" s="47"/>
+      <c r="H404" s="40"/>
       <c r="I404" s="13"/>
       <c r="J404" s="14"/>
     </row>
@@ -14498,7 +14504,7 @@
       <c r="G405" s="9">
         <v>0</v>
       </c>
-      <c r="H405" s="47"/>
+      <c r="H405" s="40"/>
       <c r="I405" s="13"/>
       <c r="J405" s="14"/>
     </row>
@@ -14524,7 +14530,7 @@
       <c r="G406" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H406" s="47"/>
+      <c r="H406" s="40"/>
       <c r="I406" s="13"/>
       <c r="J406" s="14"/>
     </row>
@@ -14550,7 +14556,7 @@
       <c r="G407" s="9">
         <v>0</v>
       </c>
-      <c r="H407" s="47"/>
+      <c r="H407" s="40"/>
       <c r="I407" s="13"/>
       <c r="J407" s="14"/>
     </row>
@@ -14576,7 +14582,7 @@
       <c r="G408" s="9">
         <v>0</v>
       </c>
-      <c r="H408" s="47"/>
+      <c r="H408" s="40"/>
       <c r="I408" s="13"/>
       <c r="J408" s="14"/>
     </row>
@@ -14602,7 +14608,7 @@
       <c r="G409" s="9">
         <v>0</v>
       </c>
-      <c r="H409" s="47"/>
+      <c r="H409" s="40"/>
       <c r="I409" s="13"/>
       <c r="J409" s="14"/>
     </row>
@@ -14628,7 +14634,7 @@
       <c r="G410" s="9">
         <v>0</v>
       </c>
-      <c r="H410" s="47"/>
+      <c r="H410" s="40"/>
       <c r="I410" s="13"/>
       <c r="J410" s="14"/>
     </row>
@@ -14654,7 +14660,7 @@
       <c r="G411" s="9">
         <v>0</v>
       </c>
-      <c r="H411" s="47"/>
+      <c r="H411" s="40"/>
       <c r="I411" s="13"/>
       <c r="J411" s="14"/>
     </row>
@@ -14680,7 +14686,7 @@
       <c r="G412" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="H412" s="47"/>
+      <c r="H412" s="40"/>
       <c r="I412" s="13"/>
       <c r="J412" s="14"/>
     </row>
@@ -14706,7 +14712,7 @@
       <c r="G413" s="9">
         <v>0</v>
       </c>
-      <c r="H413" s="47"/>
+      <c r="H413" s="40"/>
       <c r="I413" s="13"/>
       <c r="J413" s="14" t="s">
         <v>847</v>
@@ -14734,7 +14740,7 @@
       <c r="G414" s="9">
         <v>0</v>
       </c>
-      <c r="H414" s="47"/>
+      <c r="H414" s="40"/>
       <c r="I414" s="13"/>
       <c r="J414" s="14"/>
     </row>
@@ -14760,7 +14766,7 @@
       <c r="G415" s="9">
         <v>0</v>
       </c>
-      <c r="H415" s="47"/>
+      <c r="H415" s="40"/>
       <c r="I415" s="13"/>
       <c r="J415" s="14"/>
     </row>
@@ -14786,7 +14792,7 @@
       <c r="G416" s="9">
         <v>0</v>
       </c>
-      <c r="H416" s="47"/>
+      <c r="H416" s="40"/>
       <c r="I416" s="13"/>
       <c r="J416" s="14"/>
     </row>
@@ -14812,7 +14818,7 @@
       <c r="G417" s="9">
         <v>0</v>
       </c>
-      <c r="H417" s="47"/>
+      <c r="H417" s="40"/>
       <c r="I417" s="13"/>
       <c r="J417" s="14"/>
     </row>
@@ -14838,7 +14844,7 @@
       <c r="G418" s="9">
         <v>0</v>
       </c>
-      <c r="H418" s="47"/>
+      <c r="H418" s="40"/>
       <c r="I418" s="13"/>
       <c r="J418" s="14"/>
     </row>
@@ -14864,7 +14870,7 @@
       <c r="G419" s="9">
         <v>0</v>
       </c>
-      <c r="H419" s="47"/>
+      <c r="H419" s="40"/>
       <c r="I419" s="13"/>
       <c r="J419" s="14"/>
     </row>
@@ -14890,7 +14896,7 @@
       <c r="G420" s="9">
         <v>0</v>
       </c>
-      <c r="H420" s="47"/>
+      <c r="H420" s="40"/>
       <c r="I420" s="13"/>
       <c r="J420" s="14"/>
     </row>
@@ -14916,7 +14922,7 @@
       <c r="G421" s="9">
         <v>0</v>
       </c>
-      <c r="H421" s="47"/>
+      <c r="H421" s="40"/>
       <c r="I421" s="13" t="s">
         <v>486</v>
       </c>
@@ -14944,7 +14950,7 @@
       <c r="G422" s="9">
         <v>0</v>
       </c>
-      <c r="H422" s="47"/>
+      <c r="H422" s="40"/>
       <c r="I422" s="13" t="s">
         <v>488</v>
       </c>
@@ -14972,7 +14978,7 @@
       <c r="G423" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="H423" s="47"/>
+      <c r="H423" s="40"/>
       <c r="I423" s="13"/>
       <c r="J423" s="14"/>
     </row>
@@ -14998,7 +15004,7 @@
       <c r="G424" s="9">
         <v>0</v>
       </c>
-      <c r="H424" s="47"/>
+      <c r="H424" s="40"/>
       <c r="I424" s="13"/>
       <c r="J424" s="14"/>
     </row>
@@ -15024,7 +15030,7 @@
       <c r="G425" s="9">
         <v>0</v>
       </c>
-      <c r="H425" s="47"/>
+      <c r="H425" s="40"/>
       <c r="I425" s="13"/>
       <c r="J425" s="14"/>
     </row>
@@ -15050,7 +15056,7 @@
       <c r="G426" s="9">
         <v>0</v>
       </c>
-      <c r="H426" s="47"/>
+      <c r="H426" s="40"/>
       <c r="I426" s="13"/>
       <c r="J426" s="14"/>
     </row>
@@ -15076,7 +15082,7 @@
       <c r="G427" s="9">
         <v>0</v>
       </c>
-      <c r="H427" s="47"/>
+      <c r="H427" s="40"/>
       <c r="I427" s="13"/>
       <c r="J427" s="14"/>
     </row>
@@ -15102,7 +15108,7 @@
       <c r="G428" s="9">
         <v>0</v>
       </c>
-      <c r="H428" s="47"/>
+      <c r="H428" s="40"/>
       <c r="I428" s="13"/>
       <c r="J428" s="14"/>
     </row>
@@ -15128,7 +15134,7 @@
       <c r="G429" s="9">
         <v>0</v>
       </c>
-      <c r="H429" s="47"/>
+      <c r="H429" s="40"/>
       <c r="I429" s="13"/>
       <c r="J429" s="14"/>
     </row>
@@ -15154,7 +15160,7 @@
       <c r="G430" s="9">
         <v>0</v>
       </c>
-      <c r="H430" s="47"/>
+      <c r="H430" s="40"/>
       <c r="I430" s="13"/>
       <c r="J430" s="14"/>
     </row>
@@ -15180,7 +15186,7 @@
       <c r="G431" s="9">
         <v>0</v>
       </c>
-      <c r="H431" s="47"/>
+      <c r="H431" s="40"/>
       <c r="I431" s="13"/>
       <c r="J431" s="14"/>
     </row>
@@ -15206,7 +15212,7 @@
       <c r="G432" s="9">
         <v>0</v>
       </c>
-      <c r="H432" s="47"/>
+      <c r="H432" s="40"/>
       <c r="I432" s="13"/>
       <c r="J432" s="14"/>
     </row>
@@ -15232,7 +15238,7 @@
       <c r="G433" s="9">
         <v>0</v>
       </c>
-      <c r="H433" s="47"/>
+      <c r="H433" s="40"/>
       <c r="I433" s="13"/>
       <c r="J433" s="14"/>
     </row>
@@ -15258,7 +15264,7 @@
       <c r="G434" s="9">
         <v>0</v>
       </c>
-      <c r="H434" s="47"/>
+      <c r="H434" s="40"/>
       <c r="I434" s="13"/>
       <c r="J434" s="14"/>
     </row>
@@ -15284,7 +15290,7 @@
       <c r="G435" s="9">
         <v>0</v>
       </c>
-      <c r="H435" s="47"/>
+      <c r="H435" s="40"/>
       <c r="I435" s="13"/>
       <c r="J435" s="14"/>
     </row>
@@ -15310,7 +15316,7 @@
       <c r="G436" s="9">
         <v>0</v>
       </c>
-      <c r="H436" s="47"/>
+      <c r="H436" s="40"/>
       <c r="I436" s="13"/>
       <c r="J436" s="14"/>
     </row>
@@ -15336,7 +15342,7 @@
       <c r="G437" s="9">
         <v>0</v>
       </c>
-      <c r="H437" s="47"/>
+      <c r="H437" s="40"/>
       <c r="I437" s="13"/>
       <c r="J437" s="14" t="s">
         <v>848</v>
@@ -15364,7 +15370,7 @@
       <c r="G438" s="9">
         <v>0</v>
       </c>
-      <c r="H438" s="47"/>
+      <c r="H438" s="40"/>
       <c r="I438" s="13"/>
       <c r="J438" s="14"/>
     </row>
@@ -15390,7 +15396,7 @@
       <c r="G439" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="H439" s="47"/>
+      <c r="H439" s="40"/>
       <c r="I439" s="13"/>
       <c r="J439" s="14"/>
     </row>
@@ -15416,7 +15422,7 @@
       <c r="G440" s="9">
         <v>0</v>
       </c>
-      <c r="H440" s="47"/>
+      <c r="H440" s="40"/>
       <c r="I440" s="13"/>
       <c r="J440" s="14"/>
     </row>
@@ -15442,7 +15448,7 @@
       <c r="G441" s="9">
         <v>0</v>
       </c>
-      <c r="H441" s="47"/>
+      <c r="H441" s="40"/>
       <c r="I441" s="13"/>
       <c r="J441" s="14"/>
     </row>
@@ -15468,7 +15474,7 @@
       <c r="G442" s="9">
         <v>0</v>
       </c>
-      <c r="H442" s="47"/>
+      <c r="H442" s="40"/>
       <c r="I442" s="13"/>
       <c r="J442" s="14" t="s">
         <v>849</v>
@@ -15496,7 +15502,7 @@
       <c r="G443" s="9">
         <v>0</v>
       </c>
-      <c r="H443" s="47"/>
+      <c r="H443" s="40"/>
       <c r="I443" s="13"/>
       <c r="J443" s="14"/>
     </row>
@@ -15522,7 +15528,7 @@
       <c r="G444" s="9">
         <v>0</v>
       </c>
-      <c r="H444" s="47"/>
+      <c r="H444" s="40"/>
       <c r="I444" s="13"/>
       <c r="J444" s="14"/>
     </row>
@@ -15548,7 +15554,7 @@
       <c r="G445" s="9">
         <v>0</v>
       </c>
-      <c r="H445" s="47"/>
+      <c r="H445" s="40"/>
       <c r="I445" s="13"/>
       <c r="J445" s="14"/>
     </row>
@@ -15574,7 +15580,7 @@
       <c r="G446" s="9">
         <v>0</v>
       </c>
-      <c r="H446" s="47"/>
+      <c r="H446" s="40"/>
       <c r="I446" s="13"/>
       <c r="J446" s="14"/>
     </row>
@@ -15600,7 +15606,7 @@
       <c r="G447" s="9">
         <v>0</v>
       </c>
-      <c r="H447" s="47"/>
+      <c r="H447" s="40"/>
       <c r="I447" s="13"/>
       <c r="J447" s="14"/>
     </row>
@@ -15626,7 +15632,7 @@
       <c r="G448" s="9">
         <v>0</v>
       </c>
-      <c r="H448" s="47"/>
+      <c r="H448" s="40"/>
       <c r="I448" s="13"/>
       <c r="J448" s="14"/>
     </row>
@@ -15652,7 +15658,7 @@
       <c r="G449" s="9">
         <v>0</v>
       </c>
-      <c r="H449" s="47"/>
+      <c r="H449" s="40"/>
       <c r="I449" s="13"/>
       <c r="J449" s="14"/>
     </row>
@@ -15678,7 +15684,7 @@
       <c r="G450" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="H450" s="47"/>
+      <c r="H450" s="40"/>
       <c r="I450" s="13"/>
       <c r="J450" s="14"/>
     </row>
@@ -15704,7 +15710,7 @@
       <c r="G451" s="9">
         <v>0</v>
       </c>
-      <c r="H451" s="47"/>
+      <c r="H451" s="40"/>
       <c r="I451" s="13"/>
       <c r="J451" s="14"/>
     </row>
@@ -15730,7 +15736,7 @@
       <c r="G452" s="9">
         <v>0</v>
       </c>
-      <c r="H452" s="47"/>
+      <c r="H452" s="40"/>
       <c r="I452" s="13"/>
       <c r="J452" s="14"/>
     </row>
@@ -15756,7 +15762,7 @@
       <c r="G453" s="9">
         <v>0</v>
       </c>
-      <c r="H453" s="47"/>
+      <c r="H453" s="40"/>
       <c r="I453" s="13"/>
       <c r="J453" s="14"/>
     </row>
@@ -15782,7 +15788,7 @@
       <c r="G454" s="9">
         <v>0</v>
       </c>
-      <c r="H454" s="47"/>
+      <c r="H454" s="40"/>
       <c r="I454" s="13"/>
       <c r="J454" s="14"/>
     </row>
@@ -15808,7 +15814,7 @@
       <c r="G455" s="9">
         <v>0</v>
       </c>
-      <c r="H455" s="47"/>
+      <c r="H455" s="40"/>
       <c r="I455" s="13"/>
       <c r="J455" s="14"/>
     </row>
@@ -15834,7 +15840,7 @@
       <c r="G456" s="9">
         <v>0</v>
       </c>
-      <c r="H456" s="47"/>
+      <c r="H456" s="40"/>
       <c r="I456" s="13"/>
       <c r="J456" s="14"/>
     </row>
@@ -15860,7 +15866,7 @@
       <c r="G457" s="9">
         <v>0</v>
       </c>
-      <c r="H457" s="47"/>
+      <c r="H457" s="40"/>
       <c r="I457" s="13"/>
       <c r="J457" s="14"/>
     </row>
@@ -15886,7 +15892,7 @@
       <c r="G458" s="9">
         <v>0</v>
       </c>
-      <c r="H458" s="47"/>
+      <c r="H458" s="40"/>
       <c r="I458" s="13"/>
       <c r="J458" s="14"/>
     </row>
@@ -15912,7 +15918,7 @@
       <c r="G459" s="9">
         <v>0</v>
       </c>
-      <c r="H459" s="47"/>
+      <c r="H459" s="40"/>
       <c r="I459" s="13" t="s">
         <v>525</v>
       </c>
@@ -15942,7 +15948,7 @@
       <c r="G460" s="9">
         <v>0</v>
       </c>
-      <c r="H460" s="47"/>
+      <c r="H460" s="40"/>
       <c r="I460" s="13" t="s">
         <v>527</v>
       </c>
@@ -15972,7 +15978,7 @@
       <c r="G461" s="9">
         <v>0</v>
       </c>
-      <c r="H461" s="47"/>
+      <c r="H461" s="40"/>
       <c r="I461" s="13"/>
       <c r="J461" s="14"/>
     </row>
@@ -15998,7 +16004,7 @@
       <c r="G462" s="9">
         <v>0</v>
       </c>
-      <c r="H462" s="47"/>
+      <c r="H462" s="40"/>
       <c r="I462" s="13" t="s">
         <v>530</v>
       </c>
@@ -16028,7 +16034,7 @@
       <c r="G463" s="9">
         <v>0</v>
       </c>
-      <c r="H463" s="47"/>
+      <c r="H463" s="40"/>
       <c r="I463" s="13"/>
       <c r="J463" s="14"/>
     </row>
@@ -16054,7 +16060,7 @@
       <c r="G464" s="9">
         <v>0</v>
       </c>
-      <c r="H464" s="47"/>
+      <c r="H464" s="40"/>
       <c r="I464" s="13" t="s">
         <v>533</v>
       </c>
@@ -16084,7 +16090,7 @@
       <c r="G465" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="H465" s="47"/>
+      <c r="H465" s="40"/>
       <c r="I465" s="15"/>
       <c r="J465" s="16"/>
     </row>
@@ -16110,7 +16116,7 @@
       <c r="G466" s="9">
         <v>0</v>
       </c>
-      <c r="H466" s="47"/>
+      <c r="H466" s="40"/>
       <c r="I466" s="13"/>
       <c r="J466" s="14"/>
     </row>
@@ -16136,7 +16142,7 @@
       <c r="G467" s="9">
         <v>0</v>
       </c>
-      <c r="H467" s="47"/>
+      <c r="H467" s="40"/>
       <c r="I467" s="13"/>
       <c r="J467" s="14"/>
     </row>
@@ -16162,7 +16168,7 @@
       <c r="G468" s="9">
         <v>0</v>
       </c>
-      <c r="H468" s="47"/>
+      <c r="H468" s="40"/>
       <c r="I468" s="13"/>
       <c r="J468" s="14"/>
     </row>
@@ -16188,7 +16194,7 @@
       <c r="G469" s="9">
         <v>0</v>
       </c>
-      <c r="H469" s="47"/>
+      <c r="H469" s="40"/>
       <c r="I469" s="13"/>
       <c r="J469" s="14"/>
     </row>
@@ -16214,7 +16220,7 @@
       <c r="G470" s="9">
         <v>0</v>
       </c>
-      <c r="H470" s="47"/>
+      <c r="H470" s="40"/>
       <c r="I470" s="13"/>
       <c r="J470" s="14"/>
     </row>
@@ -16240,7 +16246,7 @@
       <c r="G471" s="9">
         <v>0</v>
       </c>
-      <c r="H471" s="47"/>
+      <c r="H471" s="40"/>
       <c r="I471" s="13"/>
       <c r="J471" s="14"/>
     </row>
@@ -16266,7 +16272,7 @@
       <c r="G472" s="9">
         <v>0</v>
       </c>
-      <c r="H472" s="47"/>
+      <c r="H472" s="40"/>
       <c r="I472" s="13"/>
       <c r="J472" s="14"/>
     </row>
@@ -16292,7 +16298,7 @@
       <c r="G473" s="9">
         <v>0</v>
       </c>
-      <c r="H473" s="47"/>
+      <c r="H473" s="40"/>
       <c r="I473" s="13"/>
       <c r="J473" s="14"/>
     </row>
@@ -16318,7 +16324,7 @@
       <c r="G474" s="9">
         <v>0</v>
       </c>
-      <c r="H474" s="47"/>
+      <c r="H474" s="40"/>
       <c r="I474" s="13"/>
       <c r="J474" s="14"/>
     </row>
@@ -16344,7 +16350,7 @@
       <c r="G475" s="9">
         <v>0</v>
       </c>
-      <c r="H475" s="47"/>
+      <c r="H475" s="40"/>
       <c r="I475" s="13"/>
       <c r="J475" s="14"/>
     </row>
@@ -16370,7 +16376,7 @@
       <c r="G476" s="9">
         <v>0</v>
       </c>
-      <c r="H476" s="47"/>
+      <c r="H476" s="40"/>
       <c r="I476" s="13"/>
       <c r="J476" s="14"/>
     </row>
@@ -16396,7 +16402,7 @@
       <c r="G477" s="9">
         <v>0</v>
       </c>
-      <c r="H477" s="47"/>
+      <c r="H477" s="40"/>
       <c r="I477" s="13" t="s">
         <v>546</v>
       </c>
@@ -16424,7 +16430,7 @@
       <c r="G478" s="9">
         <v>0</v>
       </c>
-      <c r="H478" s="47"/>
+      <c r="H478" s="40"/>
       <c r="I478" s="13"/>
       <c r="J478" s="14"/>
     </row>
@@ -16450,7 +16456,7 @@
       <c r="G479" s="9">
         <v>0</v>
       </c>
-      <c r="H479" s="47"/>
+      <c r="H479" s="40"/>
       <c r="I479" s="13"/>
       <c r="J479" s="14" t="s">
         <v>854</v>
@@ -16478,7 +16484,7 @@
       <c r="G480" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="H480" s="47"/>
+      <c r="H480" s="40"/>
       <c r="I480" s="13"/>
       <c r="J480" s="14"/>
     </row>
@@ -16504,7 +16510,7 @@
       <c r="G481" s="9">
         <v>0</v>
       </c>
-      <c r="H481" s="47"/>
+      <c r="H481" s="40"/>
       <c r="I481" s="13"/>
       <c r="J481" s="14"/>
     </row>
@@ -16530,7 +16536,7 @@
       <c r="G482" s="9">
         <v>0</v>
       </c>
-      <c r="H482" s="47"/>
+      <c r="H482" s="40"/>
       <c r="I482" s="13"/>
       <c r="J482" s="14"/>
     </row>
@@ -16556,7 +16562,7 @@
       <c r="G483" s="9">
         <v>0</v>
       </c>
-      <c r="H483" s="47"/>
+      <c r="H483" s="40"/>
       <c r="I483" s="13" t="s">
         <v>553</v>
       </c>
@@ -16586,7 +16592,7 @@
       <c r="G484" s="9">
         <v>0</v>
       </c>
-      <c r="H484" s="47"/>
+      <c r="H484" s="40"/>
       <c r="I484" s="13"/>
       <c r="J484" s="14"/>
     </row>
@@ -16612,7 +16618,7 @@
       <c r="G485" s="9">
         <v>0</v>
       </c>
-      <c r="H485" s="47"/>
+      <c r="H485" s="40"/>
       <c r="I485" s="13"/>
       <c r="J485" s="14"/>
     </row>
@@ -16638,7 +16644,7 @@
       <c r="G486" s="9">
         <v>0</v>
       </c>
-      <c r="H486" s="47"/>
+      <c r="H486" s="40"/>
       <c r="I486" s="13"/>
       <c r="J486" s="14"/>
     </row>
@@ -16664,7 +16670,7 @@
       <c r="G487" s="9">
         <v>0</v>
       </c>
-      <c r="H487" s="47"/>
+      <c r="H487" s="40"/>
       <c r="I487" s="13"/>
       <c r="J487" s="14"/>
     </row>
@@ -16690,7 +16696,7 @@
       <c r="G488" s="9">
         <v>0</v>
       </c>
-      <c r="H488" s="47"/>
+      <c r="H488" s="40"/>
       <c r="I488" s="13"/>
       <c r="J488" s="14"/>
     </row>
@@ -16716,7 +16722,7 @@
       <c r="G489" s="9">
         <v>0</v>
       </c>
-      <c r="H489" s="47"/>
+      <c r="H489" s="40"/>
       <c r="I489" s="13"/>
       <c r="J489" s="14"/>
     </row>
@@ -16742,7 +16748,7 @@
       <c r="G490" s="9">
         <v>0</v>
       </c>
-      <c r="H490" s="47"/>
+      <c r="H490" s="40"/>
       <c r="I490" s="13"/>
       <c r="J490" s="14"/>
     </row>
@@ -16768,7 +16774,7 @@
       <c r="G491" s="9">
         <v>0</v>
       </c>
-      <c r="H491" s="47"/>
+      <c r="H491" s="40"/>
       <c r="I491" s="13"/>
       <c r="J491" s="14"/>
     </row>
@@ -16794,7 +16800,7 @@
       <c r="G492" s="9">
         <v>0</v>
       </c>
-      <c r="H492" s="47"/>
+      <c r="H492" s="40"/>
       <c r="I492" s="13"/>
       <c r="J492" s="14"/>
     </row>
@@ -16820,7 +16826,7 @@
       <c r="G493" s="9">
         <v>0</v>
       </c>
-      <c r="H493" s="47"/>
+      <c r="H493" s="40"/>
       <c r="I493" s="13"/>
       <c r="J493" s="14"/>
     </row>
@@ -16846,7 +16852,7 @@
       <c r="G494" s="9">
         <v>0</v>
       </c>
-      <c r="H494" s="47"/>
+      <c r="H494" s="40"/>
       <c r="I494" s="13"/>
       <c r="J494" s="14"/>
     </row>
@@ -16872,7 +16878,7 @@
       <c r="G495" s="9">
         <v>0</v>
       </c>
-      <c r="H495" s="47"/>
+      <c r="H495" s="40"/>
       <c r="I495" s="13"/>
       <c r="J495" s="14"/>
     </row>
@@ -16898,7 +16904,7 @@
       <c r="G496" s="9">
         <v>0</v>
       </c>
-      <c r="H496" s="47"/>
+      <c r="H496" s="40"/>
       <c r="I496" s="13"/>
       <c r="J496" s="14"/>
     </row>
@@ -16924,7 +16930,7 @@
       <c r="G497" s="9">
         <v>0</v>
       </c>
-      <c r="H497" s="47"/>
+      <c r="H497" s="40"/>
       <c r="I497" s="13"/>
       <c r="J497" s="14"/>
     </row>
@@ -16950,7 +16956,7 @@
       <c r="G498" s="9">
         <v>0</v>
       </c>
-      <c r="H498" s="47"/>
+      <c r="H498" s="40"/>
       <c r="I498" s="13" t="s">
         <v>569</v>
       </c>
@@ -16980,7 +16986,7 @@
       <c r="G499" s="9">
         <v>0</v>
       </c>
-      <c r="H499" s="47"/>
+      <c r="H499" s="40"/>
       <c r="I499" s="13"/>
       <c r="J499" s="14"/>
     </row>
@@ -17006,7 +17012,7 @@
       <c r="G500" s="9">
         <v>0</v>
       </c>
-      <c r="H500" s="47"/>
+      <c r="H500" s="40"/>
       <c r="I500" s="13"/>
       <c r="J500" s="14"/>
     </row>
@@ -17032,7 +17038,7 @@
       <c r="G501" s="9">
         <v>0</v>
       </c>
-      <c r="H501" s="47"/>
+      <c r="H501" s="40"/>
       <c r="I501" s="13"/>
       <c r="J501" s="14"/>
     </row>
@@ -17058,7 +17064,7 @@
       <c r="G502" s="9">
         <v>0</v>
       </c>
-      <c r="H502" s="47"/>
+      <c r="H502" s="40"/>
       <c r="I502" s="13"/>
       <c r="J502" s="14"/>
     </row>
@@ -17084,7 +17090,7 @@
       <c r="G503" s="9">
         <v>0</v>
       </c>
-      <c r="H503" s="47"/>
+      <c r="H503" s="40"/>
       <c r="I503" s="13"/>
       <c r="J503" s="14"/>
     </row>
@@ -17110,7 +17116,7 @@
       <c r="G504" s="9">
         <v>0</v>
       </c>
-      <c r="H504" s="47"/>
+      <c r="H504" s="40"/>
       <c r="I504" s="13"/>
       <c r="J504" s="14" t="s">
         <v>857</v>
@@ -17138,7 +17144,7 @@
       <c r="G505" s="9">
         <v>0</v>
       </c>
-      <c r="H505" s="47"/>
+      <c r="H505" s="40"/>
       <c r="I505" s="13"/>
       <c r="J505" s="14"/>
     </row>
@@ -17164,7 +17170,7 @@
       <c r="G506" s="9">
         <v>0</v>
       </c>
-      <c r="H506" s="47"/>
+      <c r="H506" s="40"/>
       <c r="I506" s="13"/>
       <c r="J506" s="14"/>
     </row>
@@ -17190,7 +17196,7 @@
       <c r="G507" s="9">
         <v>0</v>
       </c>
-      <c r="H507" s="47"/>
+      <c r="H507" s="40"/>
       <c r="I507" s="13"/>
       <c r="J507" s="14" t="s">
         <v>858</v>
@@ -17218,7 +17224,7 @@
       <c r="G508" s="9">
         <v>0</v>
       </c>
-      <c r="H508" s="47"/>
+      <c r="H508" s="40"/>
       <c r="I508" s="13" t="s">
         <v>580</v>
       </c>
@@ -17248,7 +17254,7 @@
       <c r="G509" s="9">
         <v>0</v>
       </c>
-      <c r="H509" s="47"/>
+      <c r="H509" s="40"/>
       <c r="I509" s="13"/>
       <c r="J509" s="14"/>
     </row>
@@ -17274,7 +17280,7 @@
       <c r="G510" s="9">
         <v>0</v>
       </c>
-      <c r="H510" s="47"/>
+      <c r="H510" s="40"/>
       <c r="I510" s="13" t="s">
         <v>583</v>
       </c>
@@ -17304,7 +17310,7 @@
       <c r="G511" s="9">
         <v>0</v>
       </c>
-      <c r="H511" s="47"/>
+      <c r="H511" s="40"/>
       <c r="I511" s="13" t="s">
         <v>585</v>
       </c>
@@ -17332,7 +17338,7 @@
       <c r="G512" s="9">
         <v>0</v>
       </c>
-      <c r="H512" s="47"/>
+      <c r="H512" s="40"/>
       <c r="I512" s="13"/>
       <c r="J512" s="14"/>
     </row>
@@ -17358,7 +17364,7 @@
       <c r="G513" s="9">
         <v>0</v>
       </c>
-      <c r="H513" s="47"/>
+      <c r="H513" s="40"/>
       <c r="I513" s="13" t="s">
         <v>587</v>
       </c>
@@ -17388,7 +17394,7 @@
       <c r="G514" s="9">
         <v>0</v>
       </c>
-      <c r="H514" s="47"/>
+      <c r="H514" s="40"/>
       <c r="I514" s="13"/>
       <c r="J514" s="14"/>
     </row>
@@ -17414,7 +17420,7 @@
       <c r="G515" s="9">
         <v>0</v>
       </c>
-      <c r="H515" s="47"/>
+      <c r="H515" s="40"/>
       <c r="I515" s="13"/>
       <c r="J515" s="14"/>
     </row>
@@ -17440,7 +17446,7 @@
       <c r="G516" s="9">
         <v>0</v>
       </c>
-      <c r="H516" s="47"/>
+      <c r="H516" s="40"/>
       <c r="I516" s="13" t="s">
         <v>762</v>
       </c>
@@ -17470,7 +17476,7 @@
       <c r="G517" s="9">
         <v>0</v>
       </c>
-      <c r="H517" s="47"/>
+      <c r="H517" s="40"/>
       <c r="I517" s="13"/>
       <c r="J517" s="14"/>
     </row>
@@ -17496,7 +17502,7 @@
       <c r="G518" s="9">
         <v>0</v>
       </c>
-      <c r="H518" s="47"/>
+      <c r="H518" s="40"/>
       <c r="I518" s="13"/>
       <c r="J518" s="14"/>
     </row>
@@ -17522,7 +17528,7 @@
       <c r="G519" s="9">
         <v>0</v>
       </c>
-      <c r="H519" s="47"/>
+      <c r="H519" s="40"/>
       <c r="I519" s="13"/>
       <c r="J519" s="14"/>
     </row>
@@ -17548,7 +17554,7 @@
       <c r="G520" s="9">
         <v>0</v>
       </c>
-      <c r="H520" s="47"/>
+      <c r="H520" s="40"/>
       <c r="I520" s="13"/>
       <c r="J520" s="14"/>
     </row>
@@ -17574,7 +17580,7 @@
       <c r="G521" s="9">
         <v>0</v>
       </c>
-      <c r="H521" s="47"/>
+      <c r="H521" s="40"/>
       <c r="I521" s="13"/>
       <c r="J521" s="14" t="s">
         <v>862</v>
@@ -17602,7 +17608,7 @@
       <c r="G522" s="9">
         <v>0</v>
       </c>
-      <c r="H522" s="47"/>
+      <c r="H522" s="40"/>
       <c r="I522" s="13"/>
       <c r="J522" s="14"/>
     </row>
@@ -17628,7 +17634,7 @@
       <c r="G523" s="9">
         <v>0</v>
       </c>
-      <c r="H523" s="47"/>
+      <c r="H523" s="40"/>
       <c r="I523" s="13"/>
       <c r="J523" s="14"/>
     </row>
@@ -17654,7 +17660,7 @@
       <c r="G524" s="9">
         <v>0</v>
       </c>
-      <c r="H524" s="47"/>
+      <c r="H524" s="40"/>
       <c r="I524" s="13"/>
       <c r="J524" s="14"/>
     </row>
@@ -17680,7 +17686,7 @@
       <c r="G525" s="9">
         <v>0</v>
       </c>
-      <c r="H525" s="47"/>
+      <c r="H525" s="40"/>
       <c r="I525" s="13"/>
       <c r="J525" s="14"/>
     </row>
@@ -17706,7 +17712,7 @@
       <c r="G526" s="9">
         <v>0</v>
       </c>
-      <c r="H526" s="47"/>
+      <c r="H526" s="40"/>
       <c r="I526" s="13"/>
       <c r="J526" s="14" t="s">
         <v>863</v>
@@ -17734,7 +17740,7 @@
       <c r="G527" s="9">
         <v>0</v>
       </c>
-      <c r="H527" s="47"/>
+      <c r="H527" s="40"/>
       <c r="I527" s="13"/>
       <c r="J527" s="14"/>
     </row>
@@ -17760,7 +17766,7 @@
       <c r="G528" s="9">
         <v>0</v>
       </c>
-      <c r="H528" s="47"/>
+      <c r="H528" s="40"/>
       <c r="I528" s="13"/>
       <c r="J528" s="14"/>
     </row>
@@ -17786,7 +17792,7 @@
       <c r="G529" s="9">
         <v>0</v>
       </c>
-      <c r="H529" s="47"/>
+      <c r="H529" s="40"/>
       <c r="I529" s="13"/>
       <c r="J529" s="14"/>
     </row>
@@ -17812,7 +17818,7 @@
       <c r="G530" s="9">
         <v>0</v>
       </c>
-      <c r="H530" s="47"/>
+      <c r="H530" s="40"/>
       <c r="I530" s="13"/>
       <c r="J530" s="14"/>
     </row>
@@ -17838,7 +17844,7 @@
       <c r="G531" s="9">
         <v>0</v>
       </c>
-      <c r="H531" s="47"/>
+      <c r="H531" s="40"/>
       <c r="I531" s="13"/>
       <c r="J531" s="14"/>
     </row>
@@ -17864,7 +17870,7 @@
       <c r="G532" s="9">
         <v>0</v>
       </c>
-      <c r="H532" s="47"/>
+      <c r="H532" s="40"/>
       <c r="I532" s="13"/>
       <c r="J532" s="14"/>
     </row>
@@ -17890,7 +17896,7 @@
       <c r="G533" s="9">
         <v>0</v>
       </c>
-      <c r="H533" s="47"/>
+      <c r="H533" s="40"/>
       <c r="I533" s="13"/>
       <c r="J533" s="14"/>
     </row>
@@ -17916,7 +17922,7 @@
       <c r="G534" s="9">
         <v>0</v>
       </c>
-      <c r="H534" s="47"/>
+      <c r="H534" s="40"/>
       <c r="I534" s="13"/>
       <c r="J534" s="14"/>
     </row>
@@ -17942,7 +17948,7 @@
       <c r="G535" s="9">
         <v>0</v>
       </c>
-      <c r="H535" s="47"/>
+      <c r="H535" s="40"/>
       <c r="I535" s="13"/>
       <c r="J535" s="14"/>
     </row>
@@ -17968,7 +17974,7 @@
       <c r="G536" s="9">
         <v>0</v>
       </c>
-      <c r="H536" s="47"/>
+      <c r="H536" s="40"/>
       <c r="I536" s="13"/>
       <c r="J536" s="14"/>
     </row>
@@ -17994,7 +18000,7 @@
       <c r="G537" s="9">
         <v>0</v>
       </c>
-      <c r="H537" s="47"/>
+      <c r="H537" s="40"/>
       <c r="I537" s="13"/>
       <c r="J537" s="14"/>
     </row>
@@ -18020,7 +18026,7 @@
       <c r="G538" s="9">
         <v>0</v>
       </c>
-      <c r="H538" s="47"/>
+      <c r="H538" s="40"/>
       <c r="I538" s="13"/>
       <c r="J538" s="14"/>
     </row>
@@ -18046,7 +18052,7 @@
       <c r="G539" s="9">
         <v>0</v>
       </c>
-      <c r="H539" s="47"/>
+      <c r="H539" s="40"/>
       <c r="I539" s="13"/>
       <c r="J539" s="14"/>
     </row>
@@ -18072,7 +18078,7 @@
       <c r="G540" s="9">
         <v>0</v>
       </c>
-      <c r="H540" s="47"/>
+      <c r="H540" s="40"/>
       <c r="I540" s="13"/>
       <c r="J540" s="14"/>
     </row>
@@ -18098,7 +18104,7 @@
       <c r="G541" s="9">
         <v>0</v>
       </c>
-      <c r="H541" s="47"/>
+      <c r="H541" s="40"/>
       <c r="I541" s="13"/>
       <c r="J541" s="14"/>
     </row>
@@ -18124,7 +18130,7 @@
       <c r="G542" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="H542" s="47"/>
+      <c r="H542" s="40"/>
       <c r="I542" s="13"/>
       <c r="J542" s="14"/>
     </row>
@@ -18150,7 +18156,7 @@
       <c r="G543" s="9">
         <v>0</v>
       </c>
-      <c r="H543" s="47"/>
+      <c r="H543" s="40"/>
       <c r="I543" s="13"/>
       <c r="J543" s="14"/>
     </row>
@@ -18176,7 +18182,7 @@
       <c r="G544" s="9">
         <v>0</v>
       </c>
-      <c r="H544" s="47"/>
+      <c r="H544" s="40"/>
       <c r="I544" s="13"/>
       <c r="J544" s="14"/>
     </row>
@@ -18202,7 +18208,7 @@
       <c r="G545" s="9">
         <v>0</v>
       </c>
-      <c r="H545" s="47"/>
+      <c r="H545" s="40"/>
       <c r="I545" s="13"/>
       <c r="J545" s="14"/>
     </row>
@@ -18228,7 +18234,7 @@
       <c r="G546" s="9">
         <v>0</v>
       </c>
-      <c r="H546" s="47"/>
+      <c r="H546" s="40"/>
       <c r="I546" s="13"/>
       <c r="J546" s="14"/>
     </row>
@@ -18254,7 +18260,7 @@
       <c r="G547" s="9">
         <v>0</v>
       </c>
-      <c r="H547" s="47"/>
+      <c r="H547" s="40"/>
       <c r="I547" s="13"/>
       <c r="J547" s="14"/>
     </row>
@@ -18280,7 +18286,7 @@
       <c r="G548" s="9">
         <v>0</v>
       </c>
-      <c r="H548" s="47"/>
+      <c r="H548" s="40"/>
       <c r="I548" s="13"/>
       <c r="J548" s="14"/>
     </row>
@@ -18306,7 +18312,7 @@
       <c r="G549" s="9">
         <v>0</v>
       </c>
-      <c r="H549" s="47"/>
+      <c r="H549" s="40"/>
       <c r="I549" s="13"/>
       <c r="J549" s="14" t="s">
         <v>864</v>
@@ -18334,7 +18340,7 @@
       <c r="G550" s="9">
         <v>0</v>
       </c>
-      <c r="H550" s="47"/>
+      <c r="H550" s="40"/>
       <c r="I550" s="13" t="s">
         <v>627</v>
       </c>
@@ -18362,7 +18368,7 @@
       <c r="G551" s="9">
         <v>0</v>
       </c>
-      <c r="H551" s="47"/>
+      <c r="H551" s="40"/>
       <c r="I551" s="13"/>
       <c r="J551" s="14"/>
     </row>
@@ -18388,7 +18394,7 @@
       <c r="G552" s="9">
         <v>0</v>
       </c>
-      <c r="H552" s="47"/>
+      <c r="H552" s="40"/>
       <c r="I552" s="13"/>
       <c r="J552" s="14"/>
     </row>
@@ -18414,7 +18420,7 @@
       <c r="G553" s="9">
         <v>0</v>
       </c>
-      <c r="H553" s="47"/>
+      <c r="H553" s="40"/>
       <c r="I553" s="13"/>
       <c r="J553" s="14"/>
     </row>
@@ -18440,7 +18446,7 @@
       <c r="G554" s="9">
         <v>0</v>
       </c>
-      <c r="H554" s="47"/>
+      <c r="H554" s="40"/>
       <c r="I554" s="13"/>
       <c r="J554" s="14"/>
     </row>
@@ -18466,7 +18472,7 @@
       <c r="G555" s="9">
         <v>0</v>
       </c>
-      <c r="H555" s="47"/>
+      <c r="H555" s="40"/>
       <c r="I555" s="13"/>
       <c r="J555" s="14"/>
     </row>
@@ -18492,7 +18498,7 @@
       <c r="G556" s="9">
         <v>0</v>
       </c>
-      <c r="H556" s="47"/>
+      <c r="H556" s="40"/>
       <c r="I556" s="13"/>
       <c r="J556" s="14"/>
     </row>
@@ -18518,7 +18524,7 @@
       <c r="G557" s="9">
         <v>0</v>
       </c>
-      <c r="H557" s="47"/>
+      <c r="H557" s="40"/>
       <c r="I557" s="13"/>
       <c r="J557" s="14"/>
     </row>
@@ -18544,7 +18550,7 @@
       <c r="G558" s="9">
         <v>0</v>
       </c>
-      <c r="H558" s="47"/>
+      <c r="H558" s="40"/>
       <c r="I558" s="13"/>
       <c r="J558" s="14"/>
     </row>
@@ -18570,7 +18576,7 @@
       <c r="G559" s="9">
         <v>0</v>
       </c>
-      <c r="H559" s="47"/>
+      <c r="H559" s="40"/>
       <c r="I559" s="13"/>
       <c r="J559" s="14"/>
     </row>
@@ -18596,7 +18602,7 @@
       <c r="G560" s="9">
         <v>0</v>
       </c>
-      <c r="H560" s="47"/>
+      <c r="H560" s="40"/>
       <c r="I560" s="13"/>
       <c r="J560" s="14" t="s">
         <v>865</v>
@@ -18624,7 +18630,7 @@
       <c r="G561" s="9">
         <v>0</v>
       </c>
-      <c r="H561" s="47"/>
+      <c r="H561" s="40"/>
       <c r="I561" s="13"/>
       <c r="J561" s="14"/>
     </row>
@@ -18650,7 +18656,7 @@
       <c r="G562" s="9">
         <v>0</v>
       </c>
-      <c r="H562" s="47"/>
+      <c r="H562" s="40"/>
       <c r="I562" s="13" t="s">
         <v>640</v>
       </c>
@@ -18678,7 +18684,7 @@
       <c r="G563" s="9">
         <v>0</v>
       </c>
-      <c r="H563" s="47"/>
+      <c r="H563" s="40"/>
       <c r="I563" s="13"/>
       <c r="J563" s="14"/>
     </row>
@@ -18704,7 +18710,7 @@
       <c r="G564" s="9">
         <v>0</v>
       </c>
-      <c r="H564" s="47"/>
+      <c r="H564" s="40"/>
       <c r="I564" s="13"/>
       <c r="J564" s="14"/>
     </row>
@@ -18730,7 +18736,7 @@
       <c r="G565" s="9">
         <v>0</v>
       </c>
-      <c r="H565" s="47"/>
+      <c r="H565" s="40"/>
       <c r="I565" s="13"/>
       <c r="J565" s="14"/>
     </row>
@@ -18756,7 +18762,7 @@
       <c r="G566" s="9">
         <v>0</v>
       </c>
-      <c r="H566" s="47"/>
+      <c r="H566" s="40"/>
       <c r="I566" s="13"/>
       <c r="J566" s="14"/>
     </row>
@@ -18782,7 +18788,7 @@
       <c r="G567" s="9">
         <v>0</v>
       </c>
-      <c r="H567" s="47"/>
+      <c r="H567" s="40"/>
       <c r="I567" s="13" t="s">
         <v>646</v>
       </c>
@@ -18812,7 +18818,7 @@
       <c r="G568" s="9">
         <v>0</v>
       </c>
-      <c r="H568" s="47"/>
+      <c r="H568" s="40"/>
       <c r="I568" s="13" t="s">
         <v>648</v>
       </c>
@@ -18842,7 +18848,7 @@
       <c r="G569" s="9">
         <v>0</v>
       </c>
-      <c r="H569" s="47"/>
+      <c r="H569" s="40"/>
       <c r="I569" s="13" t="s">
         <v>650</v>
       </c>
@@ -18872,7 +18878,7 @@
       <c r="G570" s="9">
         <v>0</v>
       </c>
-      <c r="H570" s="47"/>
+      <c r="H570" s="40"/>
       <c r="I570" s="13"/>
       <c r="J570" s="14" t="s">
         <v>868</v>
@@ -18900,7 +18906,7 @@
       <c r="G571" s="9">
         <v>0</v>
       </c>
-      <c r="H571" s="47"/>
+      <c r="H571" s="40"/>
       <c r="I571" s="13" t="s">
         <v>652</v>
       </c>
@@ -18930,7 +18936,7 @@
       <c r="G572" s="9">
         <v>0</v>
       </c>
-      <c r="H572" s="47"/>
+      <c r="H572" s="40"/>
       <c r="I572" s="13"/>
       <c r="J572" s="14"/>
     </row>
@@ -18956,7 +18962,7 @@
       <c r="G573" s="9">
         <v>0</v>
       </c>
-      <c r="H573" s="47"/>
+      <c r="H573" s="40"/>
       <c r="I573" s="13"/>
       <c r="J573" s="14"/>
     </row>
@@ -18982,7 +18988,7 @@
       <c r="G574" s="9">
         <v>0</v>
       </c>
-      <c r="H574" s="47"/>
+      <c r="H574" s="40"/>
       <c r="I574" s="13"/>
       <c r="J574" s="14"/>
     </row>
@@ -19008,7 +19014,7 @@
       <c r="G575" s="9">
         <v>0</v>
       </c>
-      <c r="H575" s="47"/>
+      <c r="H575" s="40"/>
       <c r="I575" s="13"/>
       <c r="J575" s="14"/>
     </row>
@@ -19034,7 +19040,7 @@
       <c r="G576" s="9">
         <v>0</v>
       </c>
-      <c r="H576" s="47"/>
+      <c r="H576" s="40"/>
       <c r="I576" s="13"/>
       <c r="J576" s="14"/>
     </row>
@@ -19060,7 +19066,7 @@
       <c r="G577" s="9">
         <v>0</v>
       </c>
-      <c r="H577" s="47"/>
+      <c r="H577" s="40"/>
       <c r="I577" s="13"/>
       <c r="J577" s="14" t="s">
         <v>870</v>
@@ -19088,7 +19094,7 @@
       <c r="G578" s="9">
         <v>0</v>
       </c>
-      <c r="H578" s="47"/>
+      <c r="H578" s="40"/>
       <c r="I578" s="13" t="s">
         <v>763</v>
       </c>
@@ -19118,7 +19124,7 @@
       <c r="G579" s="9">
         <v>0</v>
       </c>
-      <c r="H579" s="47"/>
+      <c r="H579" s="40"/>
       <c r="I579" s="13"/>
       <c r="J579" s="14"/>
     </row>
@@ -19144,7 +19150,7 @@
       <c r="G580" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="H580" s="47"/>
+      <c r="H580" s="40"/>
       <c r="I580" s="13"/>
       <c r="J580" s="14"/>
     </row>
@@ -19170,7 +19176,7 @@
       <c r="G581" s="9">
         <v>0</v>
       </c>
-      <c r="H581" s="47"/>
+      <c r="H581" s="40"/>
       <c r="I581" s="13" t="s">
         <v>663</v>
       </c>
@@ -19200,7 +19206,7 @@
       <c r="G582" s="9">
         <v>0</v>
       </c>
-      <c r="H582" s="47"/>
+      <c r="H582" s="40"/>
       <c r="I582" s="13"/>
       <c r="J582" s="14"/>
     </row>
@@ -19226,7 +19232,7 @@
       <c r="G583" s="9">
         <v>0</v>
       </c>
-      <c r="H583" s="47"/>
+      <c r="H583" s="40"/>
       <c r="I583" s="13"/>
       <c r="J583" s="14"/>
     </row>
@@ -19252,7 +19258,7 @@
       <c r="G584" s="9">
         <v>0</v>
       </c>
-      <c r="H584" s="47"/>
+      <c r="H584" s="40"/>
       <c r="I584" s="13"/>
       <c r="J584" s="14"/>
     </row>
@@ -19278,7 +19284,7 @@
       <c r="G585" s="9">
         <v>0</v>
       </c>
-      <c r="H585" s="47"/>
+      <c r="H585" s="40"/>
       <c r="I585" s="13"/>
       <c r="J585" s="14"/>
     </row>
@@ -19304,7 +19310,7 @@
       <c r="G586" s="9">
         <v>0</v>
       </c>
-      <c r="H586" s="47"/>
+      <c r="H586" s="40"/>
       <c r="I586" s="13"/>
       <c r="J586" s="14"/>
     </row>
@@ -19330,7 +19336,7 @@
       <c r="G587" s="9">
         <v>0</v>
       </c>
-      <c r="H587" s="47"/>
+      <c r="H587" s="40"/>
       <c r="I587" s="13"/>
       <c r="J587" s="14"/>
     </row>
@@ -19356,7 +19362,7 @@
       <c r="G588" s="9">
         <v>0</v>
       </c>
-      <c r="H588" s="47"/>
+      <c r="H588" s="40"/>
       <c r="I588" s="13"/>
       <c r="J588" s="14"/>
     </row>
@@ -19382,7 +19388,7 @@
       <c r="G589" s="9">
         <v>0</v>
       </c>
-      <c r="H589" s="47"/>
+      <c r="H589" s="40"/>
       <c r="I589" s="13"/>
       <c r="J589" s="14"/>
     </row>
@@ -19408,7 +19414,7 @@
       <c r="G590" s="9">
         <v>0</v>
       </c>
-      <c r="H590" s="47"/>
+      <c r="H590" s="40"/>
       <c r="I590" s="13" t="s">
         <v>673</v>
       </c>
@@ -19436,7 +19442,7 @@
       <c r="G591" s="9">
         <v>0</v>
       </c>
-      <c r="H591" s="47"/>
+      <c r="H591" s="40"/>
       <c r="I591" s="13" t="s">
         <v>675</v>
       </c>
@@ -19466,7 +19472,7 @@
       <c r="G592" s="9">
         <v>0</v>
       </c>
-      <c r="H592" s="47"/>
+      <c r="H592" s="40"/>
       <c r="I592" s="13"/>
       <c r="J592" s="14" t="s">
         <v>873</v>
@@ -19494,7 +19500,7 @@
       <c r="G593" s="9">
         <v>0</v>
       </c>
-      <c r="H593" s="47"/>
+      <c r="H593" s="40"/>
       <c r="I593" s="13" t="s">
         <v>678</v>
       </c>
@@ -19522,7 +19528,7 @@
       <c r="G594" s="9">
         <v>0</v>
       </c>
-      <c r="H594" s="47"/>
+      <c r="H594" s="40"/>
       <c r="I594" s="13"/>
       <c r="J594" s="14"/>
     </row>
@@ -19548,7 +19554,7 @@
       <c r="G595" s="9">
         <v>0</v>
       </c>
-      <c r="H595" s="47"/>
+      <c r="H595" s="40"/>
       <c r="I595" s="13"/>
       <c r="J595" s="14"/>
     </row>
@@ -19574,7 +19580,7 @@
       <c r="G596" s="9">
         <v>0</v>
       </c>
-      <c r="H596" s="47"/>
+      <c r="H596" s="40"/>
       <c r="I596" s="13"/>
       <c r="J596" s="14" t="s">
         <v>874</v>
@@ -19602,7 +19608,7 @@
       <c r="G597" s="9">
         <v>0</v>
       </c>
-      <c r="H597" s="47"/>
+      <c r="H597" s="40"/>
       <c r="I597" s="13"/>
       <c r="J597" s="14"/>
     </row>
@@ -19628,7 +19634,7 @@
       <c r="G598" s="9">
         <v>0</v>
       </c>
-      <c r="H598" s="47"/>
+      <c r="H598" s="40"/>
       <c r="I598" s="13"/>
       <c r="J598" s="14"/>
     </row>
@@ -19654,7 +19660,7 @@
       <c r="G599" s="9">
         <v>0</v>
       </c>
-      <c r="H599" s="47"/>
+      <c r="H599" s="40"/>
       <c r="I599" s="13"/>
       <c r="J599" s="14" t="s">
         <v>875</v>
@@ -19682,7 +19688,7 @@
       <c r="G600" s="9">
         <v>0</v>
       </c>
-      <c r="H600" s="47"/>
+      <c r="H600" s="40"/>
       <c r="I600" s="13" t="s">
         <v>686</v>
       </c>
@@ -19712,7 +19718,7 @@
       <c r="G601" s="9">
         <v>0</v>
       </c>
-      <c r="H601" s="47"/>
+      <c r="H601" s="40"/>
       <c r="I601" s="13"/>
       <c r="J601" s="14"/>
     </row>
@@ -19738,7 +19744,7 @@
       <c r="G602" s="9">
         <v>0</v>
       </c>
-      <c r="H602" s="47"/>
+      <c r="H602" s="40"/>
       <c r="I602" s="13"/>
       <c r="J602" s="14"/>
     </row>
@@ -19764,7 +19770,7 @@
       <c r="G603" s="9">
         <v>0</v>
       </c>
-      <c r="H603" s="47"/>
+      <c r="H603" s="40"/>
       <c r="I603" s="13"/>
       <c r="J603" s="14"/>
     </row>
@@ -19790,7 +19796,7 @@
       <c r="G604" s="9">
         <v>0</v>
       </c>
-      <c r="H604" s="47"/>
+      <c r="H604" s="40"/>
       <c r="I604" s="13"/>
       <c r="J604" s="14"/>
     </row>
@@ -19816,7 +19822,7 @@
       <c r="G605" s="9">
         <v>0</v>
       </c>
-      <c r="H605" s="47"/>
+      <c r="H605" s="40"/>
       <c r="I605" s="13"/>
       <c r="J605" s="14"/>
     </row>
@@ -19842,7 +19848,7 @@
       <c r="G606" s="9">
         <v>0</v>
       </c>
-      <c r="H606" s="47"/>
+      <c r="H606" s="40"/>
       <c r="I606" s="13" t="s">
         <v>693</v>
       </c>
@@ -19872,7 +19878,7 @@
       <c r="G607" s="9">
         <v>0</v>
       </c>
-      <c r="H607" s="47"/>
+      <c r="H607" s="40"/>
       <c r="I607" s="13"/>
       <c r="J607" s="14"/>
     </row>
@@ -19898,7 +19904,7 @@
       <c r="G608" s="9">
         <v>0</v>
       </c>
-      <c r="H608" s="47"/>
+      <c r="H608" s="40"/>
       <c r="I608" s="13"/>
       <c r="J608" s="14"/>
     </row>
@@ -19924,7 +19930,7 @@
       <c r="G609" s="9">
         <v>0</v>
       </c>
-      <c r="H609" s="47"/>
+      <c r="H609" s="40"/>
       <c r="I609" s="13"/>
       <c r="J609" s="14" t="s">
         <v>878</v>
@@ -19952,7 +19958,7 @@
       <c r="G610" s="9">
         <v>0</v>
       </c>
-      <c r="H610" s="47"/>
+      <c r="H610" s="40"/>
       <c r="I610" s="13"/>
       <c r="J610" s="14"/>
     </row>
@@ -19978,7 +19984,7 @@
       <c r="G611" s="9">
         <v>0</v>
       </c>
-      <c r="H611" s="47"/>
+      <c r="H611" s="40"/>
       <c r="I611" s="13"/>
       <c r="J611" s="14"/>
     </row>
@@ -20004,7 +20010,7 @@
       <c r="G612" s="9">
         <v>0</v>
       </c>
-      <c r="H612" s="47"/>
+      <c r="H612" s="40"/>
       <c r="I612" s="13"/>
       <c r="J612" s="14"/>
     </row>
@@ -20030,7 +20036,7 @@
       <c r="G613" s="9">
         <v>0</v>
       </c>
-      <c r="H613" s="47"/>
+      <c r="H613" s="40"/>
       <c r="I613" s="13"/>
       <c r="J613" s="14"/>
     </row>
@@ -20056,7 +20062,7 @@
       <c r="G614" s="9">
         <v>0</v>
       </c>
-      <c r="H614" s="47"/>
+      <c r="H614" s="40"/>
       <c r="I614" s="13"/>
       <c r="J614" s="14"/>
     </row>
@@ -20082,7 +20088,7 @@
       <c r="G615" s="9">
         <v>0</v>
       </c>
-      <c r="H615" s="47"/>
+      <c r="H615" s="40"/>
       <c r="I615" s="13"/>
       <c r="J615" s="14"/>
     </row>
@@ -20108,7 +20114,7 @@
       <c r="G616" s="9">
         <v>0</v>
       </c>
-      <c r="H616" s="47"/>
+      <c r="H616" s="40"/>
       <c r="I616" s="13" t="s">
         <v>758</v>
       </c>
@@ -20136,7 +20142,7 @@
       <c r="G617" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="H617" s="47"/>
+      <c r="H617" s="40"/>
       <c r="I617" s="13"/>
       <c r="J617" s="14"/>
     </row>
@@ -20162,7 +20168,7 @@
       <c r="G618" s="9">
         <v>0</v>
       </c>
-      <c r="H618" s="47"/>
+      <c r="H618" s="40"/>
       <c r="I618" s="13" t="s">
         <v>707</v>
       </c>
@@ -20192,7 +20198,7 @@
       <c r="G619" s="9">
         <v>0</v>
       </c>
-      <c r="H619" s="47"/>
+      <c r="H619" s="40"/>
       <c r="I619" s="13" t="s">
         <v>709</v>
       </c>
@@ -20220,7 +20226,7 @@
       <c r="G620" s="9">
         <v>0</v>
       </c>
-      <c r="H620" s="47"/>
+      <c r="H620" s="40"/>
       <c r="I620" s="13"/>
       <c r="J620" s="14" t="s">
         <v>880</v>
@@ -20248,7 +20254,7 @@
       <c r="G621" s="9">
         <v>0</v>
       </c>
-      <c r="H621" s="47"/>
+      <c r="H621" s="40"/>
       <c r="I621" s="13"/>
       <c r="J621" s="14"/>
     </row>
@@ -20274,7 +20280,7 @@
       <c r="G622" s="9">
         <v>0</v>
       </c>
-      <c r="H622" s="47"/>
+      <c r="H622" s="40"/>
       <c r="I622" s="13"/>
       <c r="J622" s="14"/>
     </row>
@@ -20300,7 +20306,7 @@
       <c r="G623" s="9">
         <v>0</v>
       </c>
-      <c r="H623" s="47"/>
+      <c r="H623" s="40"/>
       <c r="I623" s="13"/>
       <c r="J623" s="14" t="s">
         <v>881</v>
@@ -20328,7 +20334,7 @@
       <c r="G624" s="9">
         <v>0</v>
       </c>
-      <c r="H624" s="47"/>
+      <c r="H624" s="40"/>
       <c r="I624" s="13"/>
       <c r="J624" s="14"/>
     </row>
@@ -20354,7 +20360,7 @@
       <c r="G625" s="9">
         <v>0</v>
       </c>
-      <c r="H625" s="47"/>
+      <c r="H625" s="40"/>
       <c r="I625" s="13"/>
       <c r="J625" s="14"/>
     </row>
@@ -20380,7 +20386,7 @@
       <c r="G626" s="9">
         <v>0</v>
       </c>
-      <c r="H626" s="47"/>
+      <c r="H626" s="40"/>
       <c r="I626" s="13"/>
       <c r="J626" s="14"/>
     </row>
@@ -20406,7 +20412,7 @@
       <c r="G627" s="9">
         <v>0</v>
       </c>
-      <c r="H627" s="47"/>
+      <c r="H627" s="40"/>
       <c r="I627" s="13"/>
       <c r="J627" s="14"/>
     </row>
@@ -20432,7 +20438,7 @@
       <c r="G628" s="9">
         <v>0</v>
       </c>
-      <c r="H628" s="47"/>
+      <c r="H628" s="40"/>
       <c r="I628" s="13" t="s">
         <v>764</v>
       </c>
@@ -20462,7 +20468,7 @@
       <c r="G629" s="9">
         <v>0</v>
       </c>
-      <c r="H629" s="47"/>
+      <c r="H629" s="40"/>
       <c r="I629" s="13"/>
       <c r="J629" s="14"/>
     </row>
@@ -20488,7 +20494,7 @@
       <c r="G630" s="9">
         <v>0</v>
       </c>
-      <c r="H630" s="47"/>
+      <c r="H630" s="40"/>
       <c r="I630" s="13"/>
       <c r="J630" s="14"/>
     </row>
@@ -20514,7 +20520,7 @@
       <c r="G631" s="9">
         <v>0</v>
       </c>
-      <c r="H631" s="47"/>
+      <c r="H631" s="40"/>
       <c r="I631" s="13" t="s">
         <v>725</v>
       </c>
@@ -20542,7 +20548,7 @@
       <c r="G632" s="9">
         <v>0</v>
       </c>
-      <c r="H632" s="47"/>
+      <c r="H632" s="40"/>
       <c r="I632" s="13"/>
       <c r="J632" s="14"/>
     </row>
@@ -20568,7 +20574,7 @@
       <c r="G633" s="9">
         <v>0</v>
       </c>
-      <c r="H633" s="47"/>
+      <c r="H633" s="40"/>
       <c r="I633" s="13"/>
       <c r="J633" s="14"/>
     </row>
@@ -20594,7 +20600,7 @@
       <c r="G634" s="9">
         <v>0</v>
       </c>
-      <c r="H634" s="47"/>
+      <c r="H634" s="40"/>
       <c r="I634" s="13" t="s">
         <v>729</v>
       </c>
@@ -20622,7 +20628,7 @@
       <c r="G635" s="9">
         <v>0</v>
       </c>
-      <c r="H635" s="47"/>
+      <c r="H635" s="40"/>
       <c r="I635" s="13"/>
       <c r="J635" s="14"/>
     </row>
@@ -20648,7 +20654,7 @@
       <c r="G636" s="9">
         <v>0</v>
       </c>
-      <c r="H636" s="47"/>
+      <c r="H636" s="40"/>
       <c r="I636" s="13"/>
       <c r="J636" s="14"/>
     </row>
@@ -20674,7 +20680,7 @@
       <c r="G637" s="9">
         <v>0</v>
       </c>
-      <c r="H637" s="47"/>
+      <c r="H637" s="40"/>
       <c r="I637" s="13"/>
       <c r="J637" s="14"/>
     </row>
@@ -20700,7 +20706,7 @@
       <c r="G638" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="H638" s="47"/>
+      <c r="H638" s="40"/>
       <c r="I638" s="13"/>
       <c r="J638" s="14"/>
     </row>
@@ -20726,7 +20732,7 @@
       <c r="G639" s="9">
         <v>0</v>
       </c>
-      <c r="H639" s="47"/>
+      <c r="H639" s="40"/>
       <c r="I639" s="13"/>
       <c r="J639" s="14"/>
     </row>
@@ -20752,7 +20758,7 @@
       <c r="G640" s="9">
         <v>0</v>
       </c>
-      <c r="H640" s="47"/>
+      <c r="H640" s="40"/>
       <c r="I640" s="13"/>
       <c r="J640" s="14"/>
     </row>
@@ -20778,7 +20784,7 @@
       <c r="G641" s="9">
         <v>0</v>
       </c>
-      <c r="H641" s="47"/>
+      <c r="H641" s="40"/>
       <c r="I641" s="13"/>
       <c r="J641" s="14"/>
     </row>
@@ -20804,7 +20810,7 @@
       <c r="G642" s="9">
         <v>0</v>
       </c>
-      <c r="H642" s="47"/>
+      <c r="H642" s="40"/>
       <c r="I642" s="13"/>
       <c r="J642" s="14" t="s">
         <v>882</v>
@@ -20832,7 +20838,7 @@
       <c r="G643" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H643" s="47"/>
+      <c r="H643" s="40"/>
       <c r="I643" s="13"/>
       <c r="J643" s="14" t="s">
         <v>883</v>
@@ -20860,7 +20866,7 @@
       <c r="G644" s="9">
         <v>0</v>
       </c>
-      <c r="H644" s="47"/>
+      <c r="H644" s="40"/>
       <c r="I644" s="13"/>
       <c r="J644" s="14"/>
     </row>
@@ -20886,7 +20892,7 @@
       <c r="G645" s="9">
         <v>0</v>
       </c>
-      <c r="H645" s="47"/>
+      <c r="H645" s="40"/>
       <c r="I645" s="13"/>
       <c r="J645" s="14"/>
     </row>
@@ -20912,7 +20918,7 @@
       <c r="G646" s="9">
         <v>0</v>
       </c>
-      <c r="H646" s="47"/>
+      <c r="H646" s="40"/>
       <c r="I646" s="13"/>
       <c r="J646" s="14"/>
     </row>
@@ -20938,7 +20944,7 @@
       <c r="G647" s="9">
         <v>0</v>
       </c>
-      <c r="H647" s="47"/>
+      <c r="H647" s="40"/>
       <c r="I647" s="13"/>
       <c r="J647" s="14"/>
     </row>
@@ -20964,7 +20970,7 @@
       <c r="G648" s="9">
         <v>0</v>
       </c>
-      <c r="H648" s="47"/>
+      <c r="H648" s="40"/>
       <c r="I648" s="13"/>
       <c r="J648" s="14"/>
     </row>
@@ -20990,7 +20996,7 @@
       <c r="G649" s="9">
         <v>0</v>
       </c>
-      <c r="H649" s="47"/>
+      <c r="H649" s="40"/>
       <c r="I649" s="13"/>
       <c r="J649" s="14"/>
     </row>
@@ -21016,7 +21022,7 @@
       <c r="G650" s="9">
         <v>0</v>
       </c>
-      <c r="H650" s="47"/>
+      <c r="H650" s="40"/>
       <c r="I650" s="13"/>
       <c r="J650" s="14" t="s">
         <v>884</v>
@@ -21044,7 +21050,7 @@
       <c r="G651" s="9">
         <v>0</v>
       </c>
-      <c r="H651" s="47"/>
+      <c r="H651" s="40"/>
       <c r="I651" s="13" t="s">
         <v>747</v>
       </c>
@@ -21072,7 +21078,7 @@
       <c r="G652" s="9">
         <v>0</v>
       </c>
-      <c r="H652" s="47"/>
+      <c r="H652" s="40"/>
       <c r="I652" s="13"/>
       <c r="J652" s="14"/>
     </row>
@@ -21098,7 +21104,7 @@
       <c r="G653" s="9">
         <v>0</v>
       </c>
-      <c r="H653" s="47"/>
+      <c r="H653" s="40"/>
       <c r="I653" s="13" t="s">
         <v>750</v>
       </c>
@@ -21128,7 +21134,7 @@
       <c r="G654" s="9">
         <v>0</v>
       </c>
-      <c r="H654" s="47"/>
+      <c r="H654" s="40"/>
       <c r="I654" s="13" t="s">
         <v>752</v>
       </c>
@@ -21158,7 +21164,7 @@
       <c r="G655" s="9">
         <v>0</v>
       </c>
-      <c r="H655" s="47"/>
+      <c r="H655" s="40"/>
       <c r="I655" s="13" t="s">
         <v>754</v>
       </c>
@@ -21188,9 +21194,9 @@
       <c r="G656" s="12">
         <v>0</v>
       </c>
-      <c r="H656" s="48"/>
-      <c r="I656" s="41"/>
-      <c r="J656" s="42"/>
+      <c r="H656" s="41"/>
+      <c r="I656" s="34"/>
+      <c r="J656" s="35"/>
     </row>
     <row r="657" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A657" s="5">
@@ -21199,26 +21205,26 @@
       <c r="B657" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C657" s="38" t="s">
+      <c r="C657" s="31" t="s">
         <v>890</v>
       </c>
-      <c r="D657" s="39" t="s">
+      <c r="D657" s="32" t="s">
         <v>890</v>
       </c>
-      <c r="E657" s="39">
-        <v>0</v>
-      </c>
-      <c r="F657" s="39">
-        <v>0</v>
-      </c>
-      <c r="G657" s="40">
-        <v>0</v>
-      </c>
-      <c r="H657" s="43" t="s">
+      <c r="E657" s="32">
+        <v>0</v>
+      </c>
+      <c r="F657" s="32">
+        <v>0</v>
+      </c>
+      <c r="G657" s="33">
+        <v>0</v>
+      </c>
+      <c r="H657" s="36" t="s">
         <v>893</v>
       </c>
-      <c r="I657" s="43"/>
-      <c r="J657" s="42"/>
+      <c r="I657" s="36"/>
+      <c r="J657" s="35"/>
     </row>
     <row r="658" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A658" s="5">
@@ -21227,24 +21233,24 @@
       <c r="B658" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C658" s="38" t="s">
+      <c r="C658" s="31" t="s">
         <v>891</v>
       </c>
-      <c r="D658" s="39" t="s">
+      <c r="D658" s="32" t="s">
         <v>891</v>
       </c>
-      <c r="E658" s="39">
-        <v>0</v>
-      </c>
-      <c r="F658" s="39">
-        <v>0</v>
-      </c>
-      <c r="G658" s="40">
-        <v>0</v>
-      </c>
-      <c r="H658" s="48"/>
-      <c r="I658" s="41"/>
-      <c r="J658" s="42"/>
+      <c r="E658" s="32">
+        <v>0</v>
+      </c>
+      <c r="F658" s="32">
+        <v>0</v>
+      </c>
+      <c r="G658" s="33">
+        <v>0</v>
+      </c>
+      <c r="H658" s="41"/>
+      <c r="I658" s="34"/>
+      <c r="J658" s="35"/>
     </row>
     <row r="659" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A659" s="5">
@@ -21253,24 +21259,24 @@
       <c r="B659" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C659" s="38" t="s">
+      <c r="C659" s="31" t="s">
         <v>892</v>
       </c>
-      <c r="D659" s="39" t="s">
+      <c r="D659" s="32" t="s">
         <v>892</v>
       </c>
-      <c r="E659" s="39">
-        <v>0</v>
-      </c>
-      <c r="F659" s="39">
-        <v>0</v>
-      </c>
-      <c r="G659" s="40">
-        <v>0</v>
-      </c>
-      <c r="H659" s="48"/>
-      <c r="I659" s="41"/>
-      <c r="J659" s="42"/>
+      <c r="E659" s="32">
+        <v>0</v>
+      </c>
+      <c r="F659" s="32">
+        <v>0</v>
+      </c>
+      <c r="G659" s="33">
+        <v>0</v>
+      </c>
+      <c r="H659" s="41"/>
+      <c r="I659" s="34"/>
+      <c r="J659" s="35"/>
     </row>
     <row r="660" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A660" s="5">
@@ -21279,26 +21285,26 @@
       <c r="B660" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C660" s="38" t="s">
+      <c r="C660" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="D660" s="38" t="s">
+      <c r="D660" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="E660" s="39">
-        <v>0</v>
-      </c>
-      <c r="F660" s="39">
-        <v>0</v>
-      </c>
-      <c r="G660" s="40">
-        <v>0</v>
-      </c>
-      <c r="H660" s="43" t="s">
+      <c r="E660" s="32">
+        <v>0</v>
+      </c>
+      <c r="F660" s="32">
+        <v>0</v>
+      </c>
+      <c r="G660" s="33">
+        <v>0</v>
+      </c>
+      <c r="H660" s="36" t="s">
         <v>897</v>
       </c>
-      <c r="I660" s="41"/>
-      <c r="J660" s="42"/>
+      <c r="I660" s="34"/>
+      <c r="J660" s="35"/>
     </row>
     <row r="661" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A661" s="5">
@@ -21307,96 +21313,112 @@
       <c r="B661" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C661" s="38" t="s">
+      <c r="C661" s="31" t="s">
         <v>895</v>
       </c>
-      <c r="D661" s="38" t="s">
+      <c r="D661" s="31" t="s">
         <v>895</v>
       </c>
-      <c r="E661" s="39">
-        <v>0</v>
-      </c>
-      <c r="F661" s="39">
-        <v>0</v>
-      </c>
-      <c r="G661" s="40">
-        <v>0</v>
-      </c>
-      <c r="H661" s="48"/>
-      <c r="I661" s="41"/>
-      <c r="J661" s="42"/>
+      <c r="E661" s="32">
+        <v>0</v>
+      </c>
+      <c r="F661" s="32">
+        <v>0</v>
+      </c>
+      <c r="G661" s="33">
+        <v>0</v>
+      </c>
+      <c r="H661" s="41"/>
+      <c r="I661" s="34"/>
+      <c r="J661" s="35"/>
     </row>
     <row r="662" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A662" s="5"/>
-      <c r="B662" s="7"/>
-      <c r="C662" s="38"/>
-      <c r="D662" s="39"/>
-      <c r="E662" s="39"/>
-      <c r="F662" s="39"/>
-      <c r="G662" s="40"/>
-      <c r="H662" s="48"/>
-      <c r="I662" s="41"/>
-      <c r="J662" s="42"/>
+      <c r="A662" s="5">
+        <v>658</v>
+      </c>
+      <c r="B662" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="C662" s="31" t="s">
+        <v>899</v>
+      </c>
+      <c r="D662" s="31" t="s">
+        <v>899</v>
+      </c>
+      <c r="E662" s="32">
+        <v>0</v>
+      </c>
+      <c r="F662" s="32">
+        <v>0</v>
+      </c>
+      <c r="G662" s="33">
+        <v>0</v>
+      </c>
+      <c r="H662" s="41" t="s">
+        <v>900</v>
+      </c>
+      <c r="I662" s="34"/>
+      <c r="J662" s="35"/>
     </row>
     <row r="663" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A663" s="5"/>
       <c r="B663" s="7"/>
-      <c r="C663" s="38"/>
-      <c r="D663" s="39"/>
-      <c r="E663" s="39"/>
-      <c r="F663" s="39"/>
-      <c r="G663" s="40"/>
-      <c r="H663" s="48"/>
-      <c r="I663" s="41"/>
-      <c r="J663" s="42"/>
+      <c r="C663" s="31"/>
+      <c r="D663" s="32"/>
+      <c r="E663" s="32"/>
+      <c r="F663" s="32"/>
+      <c r="G663" s="33"/>
+      <c r="H663" s="41"/>
+      <c r="I663" s="34"/>
+      <c r="J663" s="35"/>
     </row>
     <row r="664" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A664" s="5"/>
       <c r="B664" s="7"/>
-      <c r="C664" s="38"/>
-      <c r="D664" s="39"/>
-      <c r="E664" s="39"/>
-      <c r="F664" s="39"/>
-      <c r="G664" s="40"/>
-      <c r="H664" s="48"/>
-      <c r="I664" s="41"/>
-      <c r="J664" s="42"/>
+      <c r="C664" s="31"/>
+      <c r="D664" s="32"/>
+      <c r="E664" s="32"/>
+      <c r="F664" s="32"/>
+      <c r="G664" s="33"/>
+      <c r="H664" s="41"/>
+      <c r="I664" s="34"/>
+      <c r="J664" s="35"/>
     </row>
     <row r="665" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A665" s="5"/>
       <c r="B665" s="7"/>
-      <c r="C665" s="38"/>
-      <c r="D665" s="39"/>
-      <c r="E665" s="39"/>
-      <c r="F665" s="39"/>
-      <c r="G665" s="40"/>
-      <c r="H665" s="48"/>
-      <c r="I665" s="41"/>
-      <c r="J665" s="42"/>
+      <c r="C665" s="31"/>
+      <c r="D665" s="32"/>
+      <c r="E665" s="32"/>
+      <c r="F665" s="32"/>
+      <c r="G665" s="33"/>
+      <c r="H665" s="41"/>
+      <c r="I665" s="34"/>
+      <c r="J665" s="35"/>
     </row>
     <row r="666" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A666" s="5"/>
       <c r="B666" s="7"/>
-      <c r="C666" s="38"/>
-      <c r="D666" s="39"/>
-      <c r="E666" s="39"/>
-      <c r="F666" s="39"/>
-      <c r="G666" s="40"/>
-      <c r="H666" s="48"/>
-      <c r="I666" s="41"/>
-      <c r="J666" s="42"/>
+      <c r="C666" s="31"/>
+      <c r="D666" s="32"/>
+      <c r="E666" s="32"/>
+      <c r="F666" s="32"/>
+      <c r="G666" s="33"/>
+      <c r="H666" s="41"/>
+      <c r="I666" s="34"/>
+      <c r="J666" s="35"/>
     </row>
     <row r="667" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A667" s="5"/>
       <c r="B667" s="7"/>
-      <c r="C667" s="38"/>
-      <c r="D667" s="39"/>
-      <c r="E667" s="39"/>
-      <c r="F667" s="39"/>
-      <c r="G667" s="40"/>
-      <c r="H667" s="48"/>
-      <c r="I667" s="41"/>
-      <c r="J667" s="42"/>
+      <c r="C667" s="31"/>
+      <c r="D667" s="32"/>
+      <c r="E667" s="32"/>
+      <c r="F667" s="32"/>
+      <c r="G667" s="33"/>
+      <c r="H667" s="41"/>
+      <c r="I667" s="34"/>
+      <c r="J667" s="35"/>
     </row>
     <row r="668" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="5"/>
@@ -21406,7 +21428,7 @@
       <c r="E668" s="11"/>
       <c r="F668" s="11"/>
       <c r="G668" s="12"/>
-      <c r="H668" s="49"/>
+      <c r="H668" s="42"/>
       <c r="I668" s="29"/>
       <c r="J668" s="30"/>
     </row>
@@ -21440,7 +21462,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D655:H656 D662:H668 E661:H661 D658:H659 D657:G657 E660:G660">
+  <conditionalFormatting sqref="D655:H656 D657:G657 D658:H659 E660:G660 D663:H668 E661:H662">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
